--- a/master.xlsx
+++ b/master.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\기연리프트자료_\새 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eBroAgent\drive_mirror\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88056F3D-7F9A-4D90-B40B-E146AA131EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D97BBBF-7C49-49EA-BF68-6B426770D58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
   </bookViews>
   <sheets>
     <sheet name="계약서 " sheetId="13" r:id="rId1"/>
-    <sheet name="반입전체크리스트" sheetId="14" r:id="rId2"/>
-    <sheet name="안전점검결과서" sheetId="15" r:id="rId3"/>
+    <sheet name="반입전체크리스트" sheetId="16" r:id="rId2"/>
+    <sheet name="안전점검결과서" sheetId="17" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'계약서 '!$A$25:$K$77</definedName>
@@ -49,314 +49,314 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="366">
   <si>
     <t>계약일자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>업체명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>투입장비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수량</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>개별 임대료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>예상 사용기간</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>편도 운송료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>신청담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>성명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>핸드폰</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>사무실</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>팩   스</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비인수자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>연락처</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>투입 시간</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>현장명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>상세위치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옵션</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부착물</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고소작업대 안전수칙, 업체명판, 제원표, 운전자 주의사항, 장비작동전 주의사항, 비상하강장치작동법, 장비작동법</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>제출서류</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>특이사항</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>영업담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>T: 02-563-3220, F: 02-569-3441</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>010-6230-6864</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>A/S 대표전화</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>031-572-6240</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>010-9907-9066</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>임대인 (갑)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 임차인 (을)</t>
   </si>
   <si>
     <t>현장 상세 위치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">상호(법인명) </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>팩  스</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비 신청자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>현장 담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>품목(모델명)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>수    량</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>소계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>합계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>비    고</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부가세 별도
 /
 운송료 별도</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>운송료 청구 기준</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>옵 션</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>건설기계 사용시
 주의 사항</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 계약기간 만료후 반납통보가 없을시에는 자동으로 임대계약이 연장되며, 반납시 임차인은 장비를 운반차량에 실어 주셔야합니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 임차인의 요청에 따른 옵션 장착으로 인해 발생한 사고는 임차인이 책임집니다. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 임차인의 관리 소홀 및 과실로 발생한 장비의 파손•해체•오염등에 의한  수리비 및 훼손 복구비용은  임차인이 부담합니다. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 그외 기타 사항은 건설기계임대차 표준계약서[공정거래위원회 표준약관 제10059호]의 일반 조건에 따릅니다. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>결제 계좌</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비 인수자
 확인 서명란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">건설장비 임대계약에 따라 인도받은 임대 물건의 작동법과 관리방법을 습득한후 하자여부를 확인하여 정상적으로 사용가능한 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태에서 장비를 인수하였음을 확인합니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 인수자</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(서명)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비투입시 계약서, 반입현황, 보험증서, 안전인증서 운전기사편에 제출 바랍니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>협착방지장치, 과상승방지봉(2-원형-), 상승시 주행불가, 철망보양 후 좌측면 하단 1/2 함석보양, 확장 작업대 손잡이 부착</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>문타입, 하부 상승 금지(완전히 상승안되게), 죠이스틱커버, 죠이스틱 작동스티커, 경광등 2개</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">건설장비 임대계약에 따라 인도받은 임대 물건의 작동법과 관리방법을 습득한후 하자여부를 확인하여 정상적으로 사용가능한 </t>
+    <t>138-81-83251</t>
+  </si>
+  <si>
+    <t>등록번호</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>상태에서 장비를 인수하였음을 확인합니다.</t>
+    <t>이 수 용</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>장비 인수자</t>
+    <t>장비 번호(S/N)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 2개월 이하: 왕복 운반비 임차인 부담 ■ 4개월 이하: 편도 운반비 임차인 부담 ■ 4개월 초과 : 왕복 운반비 임대인 부담 </t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>(서명)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비투입시 계약서, 반입현황, 보험증서, 안전인증서 운전기사편에 제출 바랍니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>협착방지장치, 과상승방지봉(2-원형-), 상승시 주행불가, 철망보양 후 좌측면 하단 1/2 함석보양, 확장 작업대 손잡이 부착</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>문타입, 하부 상승 금지(완전히 상승안되게), 죠이스틱커버, 죠이스틱 작동스티커, 경광등 2개</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>138-81-83251</t>
-  </si>
-  <si>
-    <t>등록번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 수 용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 번호(S/N)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 2개월 이하: 왕복 운반비 임차인 부담 ■ 4개월 이하: 편도 운반비 임차인 부담 ■ 4개월 초과 : 왕복 운반비 임대인 부담 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>임대료
 (1대/1개월)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>영업 담당자                    ［ 김광현 과장 ］</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>영업 담당자                    ［ 김광현 과장 ］</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>고소작업대 임대차 계약서</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상     호</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>상     호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>대 표 자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">상     호 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>임대인과 임차인은 아래의 내용과 같이 임대차 계약을 체결하고, 계약서에 명시된 계약조건을 증명하기 위하여 본계약서를 2부 작성하여 각 1부씩 보관한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>임대차 계약 내용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 인도장소</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 인도 일시</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>임대차 계약 내용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 인도장소</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 인도 일시</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>임차 신청자
 (임차인의 대리인)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>첨부서류</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-334-5296</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>첨부서류</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>031-334-5296</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[운송료 
@@ -365,27 +365,27 @@
   </si>
   <si>
     <t>운송료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  본사/공장  : 경기도 용인시 처인구 포곡읍 곡현로 254-3     영업 사무소: 경기도 용인시 기흥구 기흥로 60-1, C동1004호(기흥ICT밸리)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">  본사/공장  : 경기도 용인시 처인구 포곡읍 곡현로 254-3     영업 사무소: 경기도 용인시 기흥구 기흥로 60-1, C동1004호(기흥ICT밸리)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>주식회사 기연리프트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>신한은행 140-010-007060 예금주 주식회사 기연리프트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>계약서,작동법,반입전체크리스트,안전점검결과서,안전인증서,보험증권,사업자등록증.통장사본</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>010-9402-5296</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -401,7 +401,7 @@
       </rPr>
       <t xml:space="preserve">•하차비용은 임차인이 전액 부담합니다. </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -416,80 +416,76 @@
 [평일: 09:00~18:00]
 [토요일: 09:00~17:00]</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{사업자등록번호}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>{사업자등록번호}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{고객명}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{대표자}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{현장명}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{현장주소}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{Today}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{현장담당자}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{현장담당자연락처}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{모델명}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{수량}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{SN}
 {관리번호}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{임대료}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{합계}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{옵션}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{특이사항}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{소계}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>{하차일시}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">                  (모델명: {모델명} )  ▣ 반입 전 CHECK LIST  ( 관리번호:  {관리번호}   )</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2670,14 +2666,14 @@
   <si>
     <t>※ 주의 : 1. 기준은 출고시에 점검 체크 기준이며 배터리 충전 상태에 따라 성능이 달라질 수 있습니다.
             2. 사용중 배터리의 충전상태 장비의 노후 상태에 따라 속도의 차이가 발생할 수 있습니다.</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>사업장명</t>
   </si>
   <si>
     <t>{사업장명}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>형식</t>
@@ -2685,116 +2681,108 @@
   <si>
     <t>{형식}
 고소작업대</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>제 조 사(렌탈사)</t>
   </si>
   <si>
-    <t>{제조사} (주)기연리프트</t>
-    <phoneticPr fontId="49" type="noConversion"/>
-  </si>
-  <si>
     <t>사용업체</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{고객명}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>동력전달방식</t>
   </si>
   <si>
     <t>{동력방식}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>모델명</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{모델명}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>장비중량</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{중량}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>운행속도</t>
   </si>
   <si>
     <t>{운행속도}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>작업최대높이/적재용량</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">{작업높이} </t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{적재}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>차량번호</t>
   </si>
   <si>
     <t>{차량번호}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>제조년도</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{제조연도}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>안전인증년월일</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{안전인증일}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>안전점검일시</t>
   </si>
   <si>
-    <t>{Today}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
-  </si>
-  <si>
     <t>점검부서</t>
   </si>
   <si>
     <t>정비팀</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>점검자</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>{점검자}</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>검사부분</t>
   </si>
   <si>
     <t>검사항목</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>검사결과</t>
@@ -2829,7 +2817,7 @@
   <si>
     <t>(1) 차체 및
   타이어(안정기)</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>차체의 균열, 변형, 손상 및 부식이 없을것</t>
@@ -2837,7 +2825,7 @@
   <si>
     <t>타이어의 이상마모 및 변형이 없고 구동축에서 견고하게 고정되어 있고 림부의 체결볼트, 
 너트 등이 견고하게 체결될것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>(2) 동력원</t>
@@ -2866,21 +2854,21 @@
   <si>
     <t>구조물의 균열, 변형 및 손상이 없고 힌지부 연결핀 고정상태가 양호하고 잠금밸브
 (카운터밸런스밸브)는 정상 작동되고 배관 연결부 등의 누유가 없을 것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>4. 작업대</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>(1) 낙하 및 추락 
     방호조치</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>작업대의 난간높이 1.0m 이상, 발끝막이판 높이 0.15m 이상(출입구는 0.1m 이상)이고 
 상부난간대와 발끝막이판 사이 0.55m이내의 중간대 설치할 것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>바닥면은 배수가 가능하고 미끄럼 방지 구조일 것</t>
@@ -2899,7 +2887,7 @@
   </si>
   <si>
     <t>조작한 경우에만 작동하고 해제하면 자동으로 중립위치로 복귀하고 작동방향을 문자나 기호로 명확하게 표시되어 있을것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>우발 동작을 방지하기 위한 상호 연동장치를 설치할 것
@@ -2913,7 +2901,7 @@
   </si>
   <si>
     <t>명판에는 제조자명, 모델명(형식번호), 제조번호, 제조년월, 최대작업높이, 정격하중, 허용탑승인원수, 최대허용풍속,최대허용경사, 동력원 사양, 안전인증 표시등을 표시할 것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>작업대에는 정격하중, 허용탑승인원수, 최대허용풍속(옥내용인 경우 제외)을 표시할 것</t>
@@ -2929,7 +2917,7 @@
   </si>
   <si>
     <t>전조등,미등,측등,계기판등,후퇴등,차폭등,번호등,방향지시등,제동등,작업등,속도표시등등 설치된점등 및 조명장치는 정위치에 견고하게 부착되어 손상이 없어야 하며 점등상태가 양호할 것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>⑵ 계기장치</t>
@@ -2939,7 +2927,7 @@
   </si>
   <si>
     <t>⑶ 경음기 및 경보</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>경음기 및 경보장치의 음의 크기는 기준의 범위 이내일 것</t>
@@ -2972,10 +2960,34 @@
   </si>
   <si>
     <t>동력공급이 차단되었을 때, 안전하게 작업대를 빠져 나올 수 있는 위치로 작업대를 복귀시킬 수 있는 비상 안전장치를 설치할 것</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>검사자 의견</t>
+  </si>
+  <si>
+    <t>( 모델명: {모델명} )  ▣ 반입 전 CHECK LIST  ( 관리번호: {관리번호}  )</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>점검일시</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>{점검일시}</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>{점점자}</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>{제조사} {테넌트}</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{배차일)-2} 또는 {지정}</t>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3000,13 +3012,21 @@
     <numFmt numFmtId="188" formatCode="#,##0.0000"/>
     <numFmt numFmtId="189" formatCode="\(0%\)"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5017,1220 +5037,1237 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="171">
+  <cellStyleXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="186" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="84" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="85" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="86" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="87" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="88" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="84" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="89" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="90" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="91" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="92" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="84" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="85" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="86" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="87" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="88" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="84" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="89" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="90" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="91" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="92" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="166" applyFont="1"/>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="166" applyFont="1"/>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="166" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="42" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="43" fillId="0" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="42" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="42" fillId="45" borderId="47" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="49" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="41" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="51" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="58" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="44" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="44" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="41" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="42" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="42" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="42" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="42" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="42" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="42" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="42" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="42" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="52" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="45" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="45" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="45" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="76" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="40" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="42" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="77" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="78" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="82" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="79" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="80" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="83" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="68" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="69" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="70" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="71" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="74" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="75" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="47" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="49" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="41" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="51" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="58" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="52" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="76" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="42" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="77" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="78" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="82" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="79" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="80" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="83" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="69" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="70" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="71" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="74" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="75" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="42" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="94" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="44" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="44" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="171"/>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="93" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="94" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="26" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="105" xfId="171" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="170"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="94" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="95" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="171" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="95" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="95" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="96" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="97" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="98" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="99" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="100" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="101" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="102" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="103" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="104" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="170" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="47" borderId="95" xfId="170" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="95" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="47" borderId="93" xfId="170" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="47" borderId="26" xfId="170" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="94" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="170" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="93" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="105" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="94" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="47" borderId="94" xfId="170" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="96" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="97" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="98" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="96" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="99" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="101" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="98" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="102" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="104" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="97" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="105" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="106" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="95" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="95" xfId="170" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="171">
+  <cellStyles count="172">
     <cellStyle name="20% - 강조색1 2" xfId="1" xr:uid="{7DEC5CB5-6D92-4675-8E46-5C9576ADF7D9}"/>
     <cellStyle name="20% - 강조색2 2" xfId="2" xr:uid="{7EE414B2-C914-4187-9B75-25228B8504A7}"/>
     <cellStyle name="20% - 강조색3 2" xfId="3" xr:uid="{D0588C95-6814-4684-BFF9-447CA0ED3102}"/>
@@ -6362,6 +6399,7 @@
     <cellStyle name="표준 15" xfId="128" xr:uid="{7A0183A0-FFC3-4E00-8424-F3DF80542EA5}"/>
     <cellStyle name="표준 16" xfId="129" xr:uid="{F8C8A236-0D92-4CE4-ACF5-89A80AC3AE69}"/>
     <cellStyle name="표준 17" xfId="170" xr:uid="{8F8AEB2B-87AB-4B7F-8918-72179EC87DDE}"/>
+    <cellStyle name="표준 18" xfId="171" xr:uid="{D802BB6F-D5EA-4F5E-86E7-A47F4B03442A}"/>
     <cellStyle name="표준 2" xfId="130" xr:uid="{82ACD33B-8BA0-4EC7-86C2-6BE5ADCF54AC}"/>
     <cellStyle name="표준 2 2" xfId="131" xr:uid="{736428D0-3520-46C4-B1A0-7A4768EFC124}"/>
     <cellStyle name="표준 2 2 2" xfId="132" xr:uid="{E4012327-FB6E-42E7-BF1D-E529BCFF953D}"/>
@@ -6605,6 +6643,85 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>135732</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2363A44B-E649-4578-B635-6B8C5AFE32CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7924800" y="514350"/>
+          <a:ext cx="488157" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -6623,7 +6740,7 @@
         <xdr:cNvPr id="2" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD30000F-C915-4E06-81AB-AEEEB5C1DA68}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7384EC7E-D453-444E-9F8A-A7023D365599}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6694,7 +6811,7 @@
         <xdr:cNvPr id="3" name="Rectangle 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81F00E4-1A62-4824-9733-5767839ABA3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19C82B96-1ED6-4F8D-8897-53A37ADB9E85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6765,7 +6882,7 @@
         <xdr:cNvPr id="4" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4146AB4B-6448-4890-BC55-EFDD6ADDB035}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDBE01D3-2A44-4F28-A5D7-EF0ED5AE6F1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7135,231 +7252,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="190" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="41"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="225"/>
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="228"/>
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="190" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="47"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="216"/>
+      <c r="K3" s="217"/>
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="190" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47"/>
+      <c r="B4" s="190"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="217"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="190" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="53"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="219"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="223"/>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="201"/>
+      <c r="D6" s="202"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="202"/>
+      <c r="G6" s="202"/>
+      <c r="H6" s="202"/>
+      <c r="I6" s="202"/>
+      <c r="J6" s="202"/>
+      <c r="K6" s="203"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="204"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="204"/>
+      <c r="K7" s="204"/>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="194" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="58"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="197"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="198"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A9" s="67"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="58"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="197"/>
+      <c r="H9" s="197"/>
+      <c r="I9" s="197"/>
+      <c r="J9" s="197"/>
+      <c r="K9" s="198"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A10" s="67"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="70"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="207"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="207"/>
+      <c r="J10" s="207"/>
+      <c r="K10" s="208"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A11" s="55"/>
+      <c r="A11" s="195"/>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="210"/>
+      <c r="J11" s="210"/>
+      <c r="K11" s="211"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="194" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="58"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A13" s="55"/>
+      <c r="A13" s="195"/>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="58"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
+      <c r="F13" s="197"/>
+      <c r="G13" s="197"/>
+      <c r="H13" s="197"/>
+      <c r="I13" s="197"/>
+      <c r="J13" s="197"/>
+      <c r="K13" s="198"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="199"/>
+      <c r="F14" s="199"/>
+      <c r="G14" s="199"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="199"/>
+      <c r="K14" s="199"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -7369,19 +7486,19 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
+      <c r="B15" s="190"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="200"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -7391,19 +7508,19 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="190" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
+      <c r="B16" s="190"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="187"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -7413,123 +7530,123 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="77" t="s">
+      <c r="B17" s="161"/>
+      <c r="C17" s="187" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="187"/>
+      <c r="G17" s="187"/>
+      <c r="H17" s="187"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="187"/>
+      <c r="K17" s="187"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A18" s="61"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="83" t="s">
+      <c r="A18" s="160"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="191" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="85"/>
+      <c r="D18" s="192"/>
+      <c r="E18" s="192"/>
+      <c r="F18" s="192"/>
+      <c r="G18" s="192"/>
+      <c r="H18" s="192"/>
+      <c r="I18" s="192"/>
+      <c r="J18" s="192"/>
+      <c r="K18" s="193"/>
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A19" s="74" t="s">
+      <c r="A19" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76" t="s">
+      <c r="B19" s="185"/>
+      <c r="C19" s="186" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
+      <c r="D19" s="186"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="186"/>
+      <c r="G19" s="186"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="186"/>
+      <c r="K19" s="186"/>
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="76" t="s">
+      <c r="B20" s="185"/>
+      <c r="C20" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
+      <c r="D20" s="186"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="186"/>
+      <c r="G20" s="186"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="186"/>
+      <c r="K20" s="186"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="187"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="187"/>
+      <c r="I21" s="187"/>
+      <c r="J21" s="187"/>
+      <c r="K21" s="187"/>
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="78" t="s">
+      <c r="B22" s="161"/>
+      <c r="C22" s="188" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="79"/>
-      <c r="E22" s="80" t="s">
+      <c r="D22" s="189"/>
+      <c r="E22" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="82"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="165"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="165"/>
+      <c r="K22" s="166"/>
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="86" t="s">
+      <c r="B23" s="161"/>
+      <c r="C23" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="87"/>
-      <c r="E23" s="80" t="s">
+      <c r="D23" s="163"/>
+      <c r="E23" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="82"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="165"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="165"/>
+      <c r="K23" s="166"/>
     </row>
     <row r="24" spans="1:16" ht="12" customHeight="1">
       <c r="P24" s="5"/>
@@ -7538,32 +7655,32 @@
       <c r="P25" s="5"/>
     </row>
     <row r="26" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
+      <c r="B26" s="167"/>
+      <c r="C26" s="167"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="167"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
+      <c r="J26" s="167"/>
+      <c r="K26" s="167"/>
     </row>
     <row r="27" spans="1:16" s="6" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="88"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="A27" s="167"/>
+      <c r="B27" s="167"/>
+      <c r="C27" s="167"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="167"/>
+      <c r="G27" s="167"/>
+      <c r="H27" s="167"/>
+      <c r="I27" s="167"/>
+      <c r="J27" s="167"/>
+      <c r="K27" s="167"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -7571,19 +7688,19 @@
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="168" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="B28" s="168"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="168"/>
+      <c r="E28" s="168"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="168"/>
+      <c r="H28" s="168"/>
+      <c r="I28" s="168"/>
+      <c r="J28" s="168"/>
+      <c r="K28" s="168"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -7609,29 +7726,29 @@
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="91"/>
+      <c r="B30" s="170"/>
       <c r="C30" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="96" t="s">
+      <c r="D30" s="175" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="99" t="s">
+      <c r="E30" s="176"/>
+      <c r="F30" s="177"/>
+      <c r="G30" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="91"/>
+      <c r="H30" s="170"/>
       <c r="I30" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="102" t="s">
+      <c r="J30" s="181" t="s">
         <v>85</v>
       </c>
-      <c r="K30" s="103"/>
+      <c r="K30" s="182"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -7639,93 +7756,93 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="92"/>
-      <c r="B31" s="93"/>
+      <c r="A31" s="171"/>
+      <c r="B31" s="172"/>
       <c r="C31" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="104" t="s">
+      <c r="D31" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="105"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="93"/>
+      <c r="E31" s="183"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="172"/>
       <c r="I31" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="J31" s="104" t="s">
+      <c r="J31" s="147" t="s">
         <v>86</v>
       </c>
-      <c r="K31" s="106"/>
+      <c r="K31" s="148"/>
       <c r="P31" s="8"/>
     </row>
     <row r="32" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A32" s="94"/>
-      <c r="B32" s="95"/>
+      <c r="A32" s="173"/>
+      <c r="B32" s="174"/>
       <c r="C32" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="117" t="s">
+      <c r="D32" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="118"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="101"/>
-      <c r="H32" s="95"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="174"/>
       <c r="I32" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="J32" s="120" t="s">
+      <c r="J32" s="152" t="s">
         <v>87</v>
       </c>
-      <c r="K32" s="121"/>
+      <c r="K32" s="153"/>
       <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A33" s="122" t="s">
+      <c r="A33" s="154" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="122"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="123"/>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="155"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="155"/>
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1">
-      <c r="A34" s="124"/>
-      <c r="B34" s="124"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="124"/>
-      <c r="J34" s="124"/>
-      <c r="K34" s="124"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
       <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="156" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="125"/>
-      <c r="C35" s="125"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="125"/>
-      <c r="J35" s="125"/>
-      <c r="K35" s="125"/>
+      <c r="B35" s="156"/>
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="156"/>
+      <c r="H35" s="156"/>
+      <c r="I35" s="156"/>
+      <c r="J35" s="156"/>
+      <c r="K35" s="156"/>
       <c r="P35" s="8"/>
     </row>
     <row r="36" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
@@ -7743,61 +7860,61 @@
       <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A37" s="107" t="s">
+      <c r="A37" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="108"/>
-      <c r="C37" s="109" t="s">
+      <c r="B37" s="120"/>
+      <c r="C37" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="110"/>
-      <c r="E37" s="110"/>
-      <c r="F37" s="110"/>
-      <c r="G37" s="109" t="s">
+      <c r="D37" s="142"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="141" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="111"/>
-      <c r="I37" s="112" t="s">
+      <c r="H37" s="143"/>
+      <c r="I37" s="144" t="s">
         <v>101</v>
       </c>
-      <c r="J37" s="113"/>
-      <c r="K37" s="114"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="146"/>
     </row>
     <row r="38" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A38" s="115" t="s">
+      <c r="A38" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="116"/>
-      <c r="C38" s="126" t="s">
+      <c r="B38" s="131"/>
+      <c r="C38" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="127"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="127"/>
-      <c r="K38" s="128"/>
+      <c r="D38" s="158"/>
+      <c r="E38" s="158"/>
+      <c r="F38" s="158"/>
+      <c r="G38" s="158"/>
+      <c r="H38" s="158"/>
+      <c r="I38" s="158"/>
+      <c r="J38" s="158"/>
+      <c r="K38" s="159"/>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A39" s="129" t="s">
+      <c r="A39" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="116"/>
+      <c r="B39" s="131"/>
       <c r="C39" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="132" t="s">
+      <c r="D39" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132" t="s">
+      <c r="E39" s="135"/>
+      <c r="F39" s="135"/>
+      <c r="G39" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="132"/>
+      <c r="H39" s="135"/>
       <c r="I39" s="25"/>
       <c r="J39" s="26" t="s">
         <v>32</v>
@@ -7807,75 +7924,75 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A40" s="115"/>
-      <c r="B40" s="116"/>
+      <c r="A40" s="132"/>
+      <c r="B40" s="131"/>
       <c r="C40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
-      <c r="F40" s="133"/>
-      <c r="G40" s="132" t="s">
+      <c r="D40" s="136"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="136"/>
+      <c r="G40" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
-      <c r="J40" s="132"/>
-      <c r="K40" s="134"/>
+      <c r="H40" s="135"/>
+      <c r="I40" s="135"/>
+      <c r="J40" s="135"/>
+      <c r="K40" s="137"/>
     </row>
     <row r="41" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A41" s="130"/>
-      <c r="B41" s="131"/>
+      <c r="A41" s="133"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="135" t="s">
+      <c r="D41" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="E41" s="135"/>
-      <c r="F41" s="135"/>
-      <c r="G41" s="135" t="s">
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="135"/>
-      <c r="I41" s="135" t="s">
+      <c r="H41" s="138"/>
+      <c r="I41" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="J41" s="135"/>
-      <c r="K41" s="136"/>
+      <c r="J41" s="138"/>
+      <c r="K41" s="139"/>
     </row>
     <row r="42" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="143"/>
-      <c r="J42" s="143"/>
-      <c r="K42" s="143"/>
+      <c r="A42" s="117"/>
+      <c r="B42" s="117"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
+      <c r="I42" s="117"/>
+      <c r="J42" s="117"/>
+      <c r="K42" s="117"/>
     </row>
     <row r="43" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="145"/>
+      <c r="B43" s="119"/>
       <c r="C43" s="29" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="145" t="s">
+      <c r="E43" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108" t="s">
+      <c r="F43" s="120"/>
+      <c r="G43" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="108"/>
+      <c r="H43" s="120"/>
       <c r="I43" s="30" t="s">
         <v>77</v>
       </c>
@@ -7888,485 +8005,485 @@
       <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A44" s="141" t="s">
+      <c r="A44" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="142"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="26" t="s">
         <v>94</v>
       </c>
       <c r="D44" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="137" t="s">
+      <c r="E44" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="F44" s="138"/>
-      <c r="G44" s="139" t="s">
+      <c r="F44" s="39"/>
+      <c r="G44" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="H44" s="140"/>
-      <c r="I44" s="152" t="s">
+      <c r="H44" s="116"/>
+      <c r="I44" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="J44" s="146" t="s">
+      <c r="J44" s="121" t="s">
         <v>97</v>
       </c>
-      <c r="K44" s="149" t="s">
+      <c r="K44" s="124" t="s">
         <v>40</v>
       </c>
       <c r="P44" s="8"/>
     </row>
     <row r="45" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A45" s="141"/>
-      <c r="B45" s="142"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="26"/>
       <c r="D45" s="32"/>
-      <c r="E45" s="137"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="140"/>
-      <c r="I45" s="153"/>
-      <c r="J45" s="147"/>
-      <c r="K45" s="150"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="115"/>
+      <c r="H45" s="116"/>
+      <c r="I45" s="128"/>
+      <c r="J45" s="122"/>
+      <c r="K45" s="125"/>
       <c r="P45" s="8"/>
     </row>
     <row r="46" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A46" s="141"/>
-      <c r="B46" s="142"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="26"/>
       <c r="D46" s="32"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="140"/>
-      <c r="I46" s="153"/>
-      <c r="J46" s="147"/>
-      <c r="K46" s="150"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="115"/>
+      <c r="H46" s="116"/>
+      <c r="I46" s="128"/>
+      <c r="J46" s="122"/>
+      <c r="K46" s="125"/>
       <c r="P46" s="8"/>
     </row>
     <row r="47" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A47" s="141"/>
-      <c r="B47" s="142"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="26"/>
       <c r="D47" s="32"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="153"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="150"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="115"/>
+      <c r="H47" s="116"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="122"/>
+      <c r="K47" s="125"/>
       <c r="P47" s="8"/>
     </row>
     <row r="48" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A48" s="141"/>
-      <c r="B48" s="142"/>
+      <c r="A48" s="36"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="26"/>
       <c r="D48" s="32"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="138"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="140"/>
-      <c r="I48" s="153"/>
-      <c r="J48" s="147"/>
-      <c r="K48" s="150"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="115"/>
+      <c r="H48" s="116"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="125"/>
       <c r="P48" s="8"/>
     </row>
     <row r="49" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A49" s="141"/>
-      <c r="B49" s="142"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="26"/>
       <c r="D49" s="32"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="139"/>
-      <c r="H49" s="140"/>
-      <c r="I49" s="153"/>
-      <c r="J49" s="147"/>
-      <c r="K49" s="150"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="115"/>
+      <c r="H49" s="116"/>
+      <c r="I49" s="128"/>
+      <c r="J49" s="122"/>
+      <c r="K49" s="125"/>
       <c r="P49" s="8"/>
     </row>
     <row r="50" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A50" s="141"/>
-      <c r="B50" s="142"/>
+      <c r="A50" s="36"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="26"/>
       <c r="D50" s="32"/>
-      <c r="E50" s="137"/>
-      <c r="F50" s="138"/>
-      <c r="G50" s="139"/>
-      <c r="H50" s="140"/>
-      <c r="I50" s="153"/>
-      <c r="J50" s="147"/>
-      <c r="K50" s="150"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="115"/>
+      <c r="H50" s="116"/>
+      <c r="I50" s="128"/>
+      <c r="J50" s="122"/>
+      <c r="K50" s="125"/>
       <c r="P50" s="8"/>
     </row>
     <row r="51" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A51" s="141"/>
-      <c r="B51" s="142"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="26"/>
       <c r="D51" s="32"/>
-      <c r="E51" s="137"/>
-      <c r="F51" s="138"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="140"/>
-      <c r="I51" s="153"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="150"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="115"/>
+      <c r="H51" s="116"/>
+      <c r="I51" s="128"/>
+      <c r="J51" s="122"/>
+      <c r="K51" s="125"/>
       <c r="P51" s="8"/>
     </row>
     <row r="52" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A52" s="141"/>
-      <c r="B52" s="142"/>
+      <c r="A52" s="36"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="26"/>
       <c r="D52" s="32"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="138"/>
-      <c r="G52" s="139"/>
-      <c r="H52" s="140"/>
-      <c r="I52" s="153"/>
-      <c r="J52" s="147"/>
-      <c r="K52" s="150"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="115"/>
+      <c r="H52" s="116"/>
+      <c r="I52" s="128"/>
+      <c r="J52" s="122"/>
+      <c r="K52" s="125"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A53" s="141"/>
-      <c r="B53" s="142"/>
+      <c r="A53" s="36"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="26"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="137"/>
-      <c r="F53" s="138"/>
-      <c r="G53" s="139"/>
-      <c r="H53" s="140"/>
-      <c r="I53" s="153"/>
-      <c r="J53" s="147"/>
-      <c r="K53" s="150"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="115"/>
+      <c r="H53" s="116"/>
+      <c r="I53" s="128"/>
+      <c r="J53" s="122"/>
+      <c r="K53" s="125"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A54" s="141"/>
-      <c r="B54" s="142"/>
+      <c r="A54" s="36"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="33">
         <v>0</v>
       </c>
       <c r="D54" s="32"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="138"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="140"/>
-      <c r="I54" s="153"/>
-      <c r="J54" s="147"/>
-      <c r="K54" s="150"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="115"/>
+      <c r="H54" s="116"/>
+      <c r="I54" s="128"/>
+      <c r="J54" s="122"/>
+      <c r="K54" s="125"/>
       <c r="P54" s="8"/>
     </row>
     <row r="55" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A55" s="141"/>
-      <c r="B55" s="142"/>
+      <c r="A55" s="36"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="24">
         <v>0</v>
       </c>
       <c r="D55" s="32"/>
-      <c r="E55" s="137"/>
-      <c r="F55" s="138"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="140"/>
-      <c r="I55" s="154"/>
-      <c r="J55" s="148"/>
-      <c r="K55" s="151"/>
-      <c r="N55" s="155"/>
-      <c r="O55" s="155"/>
-      <c r="P55" s="155"/>
-      <c r="Q55" s="155"/>
-      <c r="R55" s="155"/>
-      <c r="S55" s="155"/>
-      <c r="T55" s="155"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="115"/>
+      <c r="H55" s="116"/>
+      <c r="I55" s="129"/>
+      <c r="J55" s="123"/>
+      <c r="K55" s="126"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="112"/>
+      <c r="R55" s="112"/>
+      <c r="S55" s="112"/>
+      <c r="T55" s="112"/>
     </row>
     <row r="56" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A56" s="156" t="s">
+      <c r="A56" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="157"/>
-      <c r="C56" s="158" t="s">
+      <c r="B56" s="114"/>
+      <c r="C56" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="D56" s="159"/>
-      <c r="E56" s="159"/>
-      <c r="F56" s="159"/>
-      <c r="G56" s="159"/>
-      <c r="H56" s="159"/>
-      <c r="I56" s="159"/>
-      <c r="J56" s="159"/>
-      <c r="K56" s="160"/>
+      <c r="D56" s="100"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="100"/>
+      <c r="G56" s="100"/>
+      <c r="H56" s="100"/>
+      <c r="I56" s="100"/>
+      <c r="J56" s="100"/>
+      <c r="K56" s="101"/>
       <c r="P56" s="8"/>
     </row>
     <row r="57" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A57" s="180" t="s">
+      <c r="A57" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="181"/>
-      <c r="C57" s="158" t="s">
+      <c r="B57" s="98"/>
+      <c r="C57" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="D57" s="159"/>
-      <c r="E57" s="159"/>
-      <c r="F57" s="159"/>
-      <c r="G57" s="159"/>
-      <c r="H57" s="159"/>
-      <c r="I57" s="159"/>
-      <c r="J57" s="159"/>
-      <c r="K57" s="160"/>
+      <c r="D57" s="100"/>
+      <c r="E57" s="100"/>
+      <c r="F57" s="100"/>
+      <c r="G57" s="100"/>
+      <c r="H57" s="100"/>
+      <c r="I57" s="100"/>
+      <c r="J57" s="100"/>
+      <c r="K57" s="101"/>
       <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A58" s="180"/>
-      <c r="B58" s="181"/>
-      <c r="C58" s="158"/>
-      <c r="D58" s="159"/>
-      <c r="E58" s="159"/>
-      <c r="F58" s="159"/>
-      <c r="G58" s="159"/>
-      <c r="H58" s="159"/>
-      <c r="I58" s="159"/>
-      <c r="J58" s="159"/>
-      <c r="K58" s="160"/>
+      <c r="A58" s="97"/>
+      <c r="B58" s="98"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="100"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="100"/>
+      <c r="J58" s="100"/>
+      <c r="K58" s="101"/>
     </row>
     <row r="59" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A59" s="182" t="s">
+      <c r="A59" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="B59" s="183"/>
-      <c r="C59" s="184" t="s">
+      <c r="B59" s="103"/>
+      <c r="C59" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="D59" s="185"/>
-      <c r="E59" s="185"/>
-      <c r="F59" s="185"/>
-      <c r="G59" s="185"/>
-      <c r="H59" s="185"/>
-      <c r="I59" s="185"/>
-      <c r="J59" s="185"/>
-      <c r="K59" s="186"/>
+      <c r="D59" s="105"/>
+      <c r="E59" s="105"/>
+      <c r="F59" s="105"/>
+      <c r="G59" s="105"/>
+      <c r="H59" s="105"/>
+      <c r="I59" s="105"/>
+      <c r="J59" s="105"/>
+      <c r="K59" s="106"/>
     </row>
     <row r="60" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A60" s="187" t="s">
+      <c r="A60" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="188"/>
-      <c r="C60" s="184" t="s">
+      <c r="B60" s="108"/>
+      <c r="C60" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="185"/>
-      <c r="E60" s="185"/>
-      <c r="F60" s="185"/>
-      <c r="G60" s="185"/>
-      <c r="H60" s="185"/>
-      <c r="I60" s="185"/>
-      <c r="J60" s="185"/>
-      <c r="K60" s="186"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
     </row>
     <row r="61" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A61" s="189"/>
-      <c r="B61" s="190"/>
-      <c r="C61" s="191"/>
-      <c r="D61" s="192"/>
-      <c r="E61" s="192"/>
-      <c r="F61" s="192"/>
-      <c r="G61" s="192"/>
-      <c r="H61" s="192"/>
-      <c r="I61" s="192"/>
-      <c r="J61" s="192"/>
-      <c r="K61" s="193"/>
+      <c r="A61" s="67"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="109"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="110"/>
+      <c r="G61" s="110"/>
+      <c r="H61" s="110"/>
+      <c r="I61" s="110"/>
+      <c r="J61" s="110"/>
+      <c r="K61" s="111"/>
     </row>
     <row r="62" spans="1:20" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A62" s="124"/>
-      <c r="B62" s="124"/>
-      <c r="C62" s="124"/>
-      <c r="D62" s="124"/>
-      <c r="E62" s="124"/>
-      <c r="F62" s="124"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="124"/>
-      <c r="I62" s="124"/>
-      <c r="J62" s="124"/>
-      <c r="K62" s="124"/>
+      <c r="A62" s="58"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="58"/>
       <c r="P62" s="8"/>
     </row>
     <row r="63" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="161" t="s">
+      <c r="A63" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="162"/>
-      <c r="C63" s="169" t="s">
+      <c r="B63" s="79"/>
+      <c r="C63" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="D63" s="170"/>
-      <c r="E63" s="170"/>
-      <c r="F63" s="170"/>
-      <c r="G63" s="170"/>
-      <c r="H63" s="170"/>
-      <c r="I63" s="170"/>
-      <c r="J63" s="170"/>
-      <c r="K63" s="171"/>
+      <c r="D63" s="87"/>
+      <c r="E63" s="87"/>
+      <c r="F63" s="87"/>
+      <c r="G63" s="87"/>
+      <c r="H63" s="87"/>
+      <c r="I63" s="87"/>
+      <c r="J63" s="87"/>
+      <c r="K63" s="88"/>
       <c r="P63" s="8"/>
     </row>
     <row r="64" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="163"/>
-      <c r="B64" s="164"/>
-      <c r="C64" s="172" t="s">
+      <c r="A64" s="80"/>
+      <c r="B64" s="81"/>
+      <c r="C64" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="173"/>
-      <c r="E64" s="173"/>
-      <c r="F64" s="173"/>
-      <c r="G64" s="173"/>
-      <c r="H64" s="173"/>
-      <c r="I64" s="173"/>
-      <c r="J64" s="173"/>
-      <c r="K64" s="174"/>
+      <c r="D64" s="90"/>
+      <c r="E64" s="90"/>
+      <c r="F64" s="90"/>
+      <c r="G64" s="90"/>
+      <c r="H64" s="90"/>
+      <c r="I64" s="90"/>
+      <c r="J64" s="90"/>
+      <c r="K64" s="91"/>
       <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="163"/>
-      <c r="B65" s="164"/>
-      <c r="C65" s="175" t="s">
+      <c r="A65" s="80"/>
+      <c r="B65" s="81"/>
+      <c r="C65" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="175"/>
-      <c r="E65" s="175"/>
-      <c r="F65" s="175"/>
-      <c r="G65" s="175"/>
-      <c r="H65" s="175"/>
-      <c r="I65" s="175"/>
-      <c r="J65" s="175"/>
-      <c r="K65" s="176"/>
+      <c r="D65" s="92"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
+      <c r="J65" s="92"/>
+      <c r="K65" s="93"/>
       <c r="P65" s="8"/>
     </row>
     <row r="66" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="165"/>
-      <c r="B66" s="166"/>
-      <c r="C66" s="175" t="s">
+      <c r="A66" s="82"/>
+      <c r="B66" s="83"/>
+      <c r="C66" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="175"/>
-      <c r="E66" s="175"/>
-      <c r="F66" s="175"/>
-      <c r="G66" s="175"/>
-      <c r="H66" s="175"/>
-      <c r="I66" s="175"/>
-      <c r="J66" s="175"/>
-      <c r="K66" s="176"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="92"/>
+      <c r="K66" s="93"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A67" s="167"/>
-      <c r="B67" s="168"/>
-      <c r="C67" s="177" t="s">
+      <c r="A67" s="84"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="178"/>
-      <c r="E67" s="178"/>
-      <c r="F67" s="178"/>
-      <c r="G67" s="178"/>
-      <c r="H67" s="178"/>
-      <c r="I67" s="178"/>
-      <c r="J67" s="178"/>
-      <c r="K67" s="179"/>
+      <c r="D67" s="95"/>
+      <c r="E67" s="95"/>
+      <c r="F67" s="95"/>
+      <c r="G67" s="95"/>
+      <c r="H67" s="95"/>
+      <c r="I67" s="95"/>
+      <c r="J67" s="95"/>
+      <c r="K67" s="96"/>
       <c r="P67" s="8"/>
     </row>
     <row r="68" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A68" s="124"/>
-      <c r="B68" s="124"/>
-      <c r="C68" s="124"/>
-      <c r="D68" s="124"/>
-      <c r="E68" s="124"/>
-      <c r="F68" s="124"/>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
+      <c r="A68" s="58"/>
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
+      <c r="J68" s="58"/>
+      <c r="K68" s="58"/>
     </row>
     <row r="69" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A69" s="212" t="s">
+      <c r="A69" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="B69" s="213"/>
-      <c r="C69" s="214" t="s">
+      <c r="B69" s="60"/>
+      <c r="C69" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="D69" s="214"/>
-      <c r="E69" s="214"/>
-      <c r="F69" s="214"/>
-      <c r="G69" s="214"/>
-      <c r="H69" s="214"/>
-      <c r="I69" s="214"/>
-      <c r="J69" s="214"/>
-      <c r="K69" s="215"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="61"/>
+      <c r="K69" s="62"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A70" s="124"/>
-      <c r="B70" s="124"/>
-      <c r="C70" s="124"/>
-      <c r="D70" s="124"/>
-      <c r="E70" s="124"/>
-      <c r="F70" s="124"/>
-      <c r="G70" s="124"/>
-      <c r="H70" s="124"/>
-      <c r="I70" s="124"/>
-      <c r="J70" s="124"/>
-      <c r="K70" s="124"/>
+      <c r="A70" s="58"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="58"/>
+      <c r="K70" s="58"/>
     </row>
     <row r="71" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="216" t="s">
+      <c r="A71" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="217"/>
-      <c r="C71" s="220" t="s">
+      <c r="B71" s="64"/>
+      <c r="C71" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D71" s="220"/>
-      <c r="E71" s="220"/>
-      <c r="F71" s="220"/>
-      <c r="G71" s="220"/>
-      <c r="H71" s="220"/>
-      <c r="I71" s="220"/>
-      <c r="J71" s="220"/>
-      <c r="K71" s="221"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="70"/>
     </row>
     <row r="72" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A72" s="218"/>
-      <c r="B72" s="219"/>
-      <c r="C72" s="222" t="s">
+      <c r="A72" s="65"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="222"/>
-      <c r="E72" s="222"/>
-      <c r="F72" s="222"/>
-      <c r="G72" s="222"/>
-      <c r="H72" s="222"/>
-      <c r="I72" s="222"/>
-      <c r="J72" s="222"/>
-      <c r="K72" s="223"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="71"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="71"/>
+      <c r="H72" s="71"/>
+      <c r="I72" s="71"/>
+      <c r="J72" s="71"/>
+      <c r="K72" s="72"/>
     </row>
     <row r="73" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A73" s="189"/>
-      <c r="B73" s="190"/>
+      <c r="A73" s="67"/>
+      <c r="B73" s="68"/>
       <c r="C73" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="224" t="s">
+      <c r="D73" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="E73" s="225"/>
-      <c r="F73" s="226"/>
-      <c r="G73" s="227" t="s">
+      <c r="E73" s="74"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="227"/>
-      <c r="I73" s="227"/>
-      <c r="J73" s="227"/>
-      <c r="K73" s="228"/>
+      <c r="H73" s="76"/>
+      <c r="I73" s="76"/>
+      <c r="J73" s="76"/>
+      <c r="K73" s="77"/>
     </row>
     <row r="74" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
       <c r="A74" s="35"/>
@@ -8382,53 +8499,53 @@
       <c r="K74" s="35"/>
     </row>
     <row r="75" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A75" s="194" t="s">
+      <c r="A75" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="195"/>
-      <c r="C75" s="195"/>
-      <c r="D75" s="195"/>
-      <c r="E75" s="195"/>
-      <c r="F75" s="195"/>
-      <c r="G75" s="195"/>
-      <c r="H75" s="195"/>
-      <c r="I75" s="195"/>
-      <c r="J75" s="195"/>
-      <c r="K75" s="196"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+      <c r="K75" s="42"/>
     </row>
     <row r="76" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A76" s="197" t="s">
+      <c r="A76" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="198"/>
-      <c r="C76" s="199"/>
-      <c r="D76" s="203" t="s">
+      <c r="B76" s="44"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="204"/>
-      <c r="F76" s="204"/>
-      <c r="G76" s="204"/>
-      <c r="H76" s="207" t="s">
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
+      <c r="H76" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="I76" s="207"/>
-      <c r="J76" s="209" t="s">
+      <c r="I76" s="53"/>
+      <c r="J76" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K76" s="210"/>
+      <c r="K76" s="56"/>
     </row>
     <row r="77" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A77" s="200"/>
-      <c r="B77" s="201"/>
-      <c r="C77" s="202"/>
-      <c r="D77" s="205"/>
-      <c r="E77" s="206"/>
-      <c r="F77" s="206"/>
-      <c r="G77" s="206"/>
-      <c r="H77" s="208"/>
-      <c r="I77" s="208"/>
-      <c r="J77" s="205"/>
-      <c r="K77" s="211"/>
+      <c r="A77" s="46"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="54"/>
+      <c r="I77" s="54"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="57"/>
     </row>
     <row r="78" spans="1:16">
       <c r="D78" s="5" t="s">
@@ -8437,58 +8554,87 @@
     </row>
   </sheetData>
   <mergeCells count="157">
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A76:C77"/>
-    <mergeCell ref="D76:G77"/>
-    <mergeCell ref="H76:I77"/>
-    <mergeCell ref="J76:K77"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:K69"/>
-    <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:K71"/>
-    <mergeCell ref="C72:K72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A63:B67"/>
-    <mergeCell ref="C63:K63"/>
-    <mergeCell ref="C64:K64"/>
-    <mergeCell ref="C65:K65"/>
-    <mergeCell ref="C66:K66"/>
-    <mergeCell ref="C67:K67"/>
-    <mergeCell ref="A57:B58"/>
-    <mergeCell ref="C57:K57"/>
-    <mergeCell ref="C58:K58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="A60:B61"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="C61:K61"/>
-    <mergeCell ref="N55:T55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:K56"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="A26:K27"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A30:B32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H32"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="A39:B41"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="A51:B51"/>
@@ -8513,89 +8659,60 @@
     <mergeCell ref="G47:H47"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="G49:H49"/>
-    <mergeCell ref="A39:B41"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="C38:K38"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="A26:K27"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A30:B32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H32"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N55:T55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A63:B67"/>
+    <mergeCell ref="C63:K63"/>
+    <mergeCell ref="C64:K64"/>
+    <mergeCell ref="C65:K65"/>
+    <mergeCell ref="C66:K66"/>
+    <mergeCell ref="C67:K67"/>
+    <mergeCell ref="A57:B58"/>
+    <mergeCell ref="C57:K57"/>
+    <mergeCell ref="C58:K58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="A60:B61"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A76:C77"/>
+    <mergeCell ref="D76:G77"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="J76:K77"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:K69"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="C72:K72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:E3 J3" xr:uid="{3AD5D325-B066-4F33-B497-1D587D6DD12E}"/>
   </dataValidations>
@@ -8608,32 +8725,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5698F315-2677-46F6-8329-8A56B08D41DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73D97268-9CB9-46C6-8D6E-31F0AF097715}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L46"/>
+  <dimension ref="B2:N46"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="232" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" style="232" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="232" customWidth="1"/>
-    <col min="4" max="5" width="6.85546875" style="232" customWidth="1"/>
-    <col min="6" max="6" width="8" style="232" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" style="232" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="232" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="232" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" style="232" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" style="232" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="232" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="232"/>
+    <col min="1" max="1" width="1.85546875" style="232" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="232" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="232" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="232" customWidth="1"/>
+    <col min="5" max="6" width="6.85546875" style="232" customWidth="1"/>
+    <col min="7" max="7" width="8" style="232" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" style="232" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" style="232" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="232" customWidth="1"/>
+    <col min="11" max="11" width="6.85546875" style="232" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="232" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" style="232" customWidth="1"/>
+    <col min="14" max="14" width="1.85546875" style="232" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="232"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="229" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="230"/>
+    <row r="2" spans="2:14" ht="33.950000000000003" customHeight="1">
+      <c r="B2" s="229" t="s">
+        <v>360</v>
+      </c>
       <c r="C2" s="230"/>
       <c r="D2" s="230"/>
       <c r="E2" s="230"/>
@@ -8643,1342 +8761,1355 @@
       <c r="I2" s="230"/>
       <c r="J2" s="230"/>
       <c r="K2" s="230"/>
-      <c r="L2" s="231"/>
-    </row>
-    <row r="3" spans="1:12" ht="27.95" customHeight="1">
-      <c r="A3" s="233"/>
-      <c r="B3" s="234"/>
+      <c r="L2" s="230"/>
+      <c r="M2" s="231"/>
+    </row>
+    <row r="3" spans="2:14" ht="21" customHeight="1">
+      <c r="B3" s="233" t="s">
+        <v>361</v>
+      </c>
       <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="234"/>
-      <c r="H3" s="234"/>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="235"/>
-    </row>
-    <row r="4" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A4" s="236" t="s">
+      <c r="D3" s="235" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
+      <c r="G3" s="237"/>
+      <c r="H3" s="238"/>
+      <c r="I3" s="239" t="s">
+        <v>302</v>
+      </c>
+      <c r="J3" s="240" t="s">
+        <v>363</v>
+      </c>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="M3" s="241"/>
+      <c r="N3" s="242"/>
+    </row>
+    <row r="4" spans="2:14" ht="21.95" customHeight="1">
+      <c r="B4" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="244" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="D4" s="245"/>
+      <c r="E4" s="244" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="D4" s="237" t="s">
+      <c r="F4" s="245"/>
+      <c r="G4" s="246" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="238"/>
-      <c r="F4" s="239" t="s">
+      <c r="H4" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="239" t="s">
+      <c r="I4" s="244" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="237" t="s">
+      <c r="J4" s="245"/>
+      <c r="K4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="238"/>
-      <c r="J4" s="237" t="s">
+      <c r="L4" s="245"/>
+      <c r="M4" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="238"/>
-      <c r="L4" s="239" t="s">
+    </row>
+    <row r="5" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B5" s="247" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A5" s="233" t="s">
+      <c r="C5" s="248"/>
+      <c r="D5" s="246" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="235"/>
-      <c r="C5" s="239" t="s">
+      <c r="E5" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="239" t="s">
+      <c r="F5" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="239" t="s">
+      <c r="G5" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="239" t="s">
+      <c r="H5" s="247" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="233" t="s">
+      <c r="I5" s="248"/>
+      <c r="J5" s="246" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="L5" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="M5" s="246" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B6" s="243" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="235"/>
-      <c r="I5" s="239" t="s">
+      <c r="C6" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="246"/>
+      <c r="F6" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="249" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="243" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="J6" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="246"/>
+      <c r="L6" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="249" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B7" s="243" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="243" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="246"/>
+      <c r="F7" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="250"/>
+      <c r="H7" s="243" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="243" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M7" s="250"/>
+    </row>
+    <row r="8" spans="2:14" ht="15.95" customHeight="1">
+      <c r="B8" s="243" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="243" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="246"/>
+      <c r="F8" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="250"/>
+      <c r="H8" s="243" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="243" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="246" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="246"/>
+      <c r="L8" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="250"/>
+    </row>
+    <row r="9" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B9" s="243" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="243" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="250"/>
+      <c r="H9" s="243" t="s">
+        <v>137</v>
+      </c>
+      <c r="I9" s="243" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="246" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="246" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="246" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="250"/>
+    </row>
+    <row r="10" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B10" s="243" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="243" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="250"/>
+      <c r="H10" s="243" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="243" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="250"/>
+    </row>
+    <row r="11" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B11" s="243" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="243" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="250"/>
+      <c r="H11" s="243" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="243" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11" s="250"/>
+    </row>
+    <row r="12" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B12" s="243" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="243" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="246"/>
+      <c r="F12" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="250"/>
+      <c r="H12" s="243" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="243" t="s">
+        <v>153</v>
+      </c>
+      <c r="J12" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="246"/>
+      <c r="L12" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12" s="251"/>
+    </row>
+    <row r="13" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B13" s="243" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="243" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="250"/>
+      <c r="H13" s="247" t="s">
+        <v>156</v>
+      </c>
+      <c r="I13" s="248"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="239" t="s">
+      <c r="L13" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="239" t="s">
+      <c r="M13" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="L5" s="239" t="s">
+    </row>
+    <row r="14" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B14" s="243" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="243" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="251"/>
+      <c r="H14" s="243" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="243" t="s">
+        <v>160</v>
+      </c>
+      <c r="J14" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" s="249" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="17.100000000000001" customHeight="1">
+      <c r="B15" s="247" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="248"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="246" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" s="243" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="243" t="s">
+        <v>164</v>
+      </c>
+      <c r="J15" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="250"/>
+    </row>
+    <row r="16" spans="2:14" ht="15.95" customHeight="1">
+      <c r="B16" s="243" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="243" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="249" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="243" t="s">
+        <v>167</v>
+      </c>
+      <c r="I16" s="243" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" s="250"/>
+    </row>
+    <row r="17" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B17" s="243" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="243" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="250"/>
+      <c r="H17" s="243" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="243" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="250"/>
+    </row>
+    <row r="18" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B18" s="243" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="243" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="250"/>
+      <c r="H18" s="243" t="s">
+        <v>175</v>
+      </c>
+      <c r="I18" s="243" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" s="250"/>
+    </row>
+    <row r="19" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B19" s="243" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="243" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="246"/>
+      <c r="F19" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="251"/>
+      <c r="H19" s="243" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="243" t="s">
+        <v>180</v>
+      </c>
+      <c r="J19" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="246"/>
+      <c r="L19" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M19" s="250"/>
+    </row>
+    <row r="20" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B20" s="247" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="248"/>
+      <c r="D20" s="246"/>
+      <c r="E20" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="246" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="243" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="243" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="246"/>
+      <c r="L20" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="M20" s="250"/>
+    </row>
+    <row r="21" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B21" s="243" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="243" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="249" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="243" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="243" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21" s="250"/>
+    </row>
+    <row r="22" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B22" s="243" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="243" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="246"/>
+      <c r="F22" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="250"/>
+      <c r="H22" s="243" t="s">
+        <v>189</v>
+      </c>
+      <c r="I22" s="243" t="s">
+        <v>190</v>
+      </c>
+      <c r="J22" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="246"/>
+      <c r="L22" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M22" s="250"/>
+    </row>
+    <row r="23" spans="2:13" ht="15.95" customHeight="1">
+      <c r="B23" s="243" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="243" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="250"/>
+      <c r="H23" s="243" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="243" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K23" s="246"/>
+      <c r="L23" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M23" s="250"/>
+    </row>
+    <row r="24" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B24" s="243" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="243" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="246"/>
+      <c r="F24" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="251"/>
+      <c r="H24" s="243" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24" s="243" t="s">
+        <v>198</v>
+      </c>
+      <c r="J24" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K24" s="246"/>
+      <c r="L24" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M24" s="250"/>
+    </row>
+    <row r="25" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B25" s="247" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="248"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="246" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="243" t="s">
+        <v>200</v>
+      </c>
+      <c r="I25" s="243" t="s">
+        <v>201</v>
+      </c>
+      <c r="J25" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25" s="250"/>
+    </row>
+    <row r="26" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B26" s="243" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="243" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="249" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="243" t="s">
+        <v>204</v>
+      </c>
+      <c r="I26" s="243" t="s">
+        <v>205</v>
+      </c>
+      <c r="J26" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M26" s="250"/>
+    </row>
+    <row r="27" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B27" s="243" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="243" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="250"/>
+      <c r="H27" s="243" t="s">
+        <v>208</v>
+      </c>
+      <c r="I27" s="243" t="s">
+        <v>209</v>
+      </c>
+      <c r="J27" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M27" s="251"/>
+    </row>
+    <row r="28" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B28" s="243" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="243" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="246"/>
+      <c r="F28" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="250"/>
+      <c r="H28" s="247" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="248"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="L28" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="M28" s="246" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B29" s="243" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="243" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" s="250"/>
+      <c r="H29" s="243" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="243" t="s">
+        <v>216</v>
+      </c>
+      <c r="J29" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K29" s="246"/>
+      <c r="L29" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M29" s="249" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B30" s="243" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="243" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="246"/>
+      <c r="F30" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G30" s="250"/>
+      <c r="H30" s="243" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="243" t="s">
+        <v>220</v>
+      </c>
+      <c r="J30" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K30" s="246"/>
+      <c r="L30" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30" s="250"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.95" customHeight="1">
+      <c r="B31" s="243" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="243" t="s">
+        <v>222</v>
+      </c>
+      <c r="D31" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="250"/>
+      <c r="H31" s="243" t="s">
+        <v>223</v>
+      </c>
+      <c r="I31" s="243" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M31" s="250"/>
+    </row>
+    <row r="32" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B32" s="243" t="s">
+        <v>225</v>
+      </c>
+      <c r="C32" s="243" t="s">
+        <v>226</v>
+      </c>
+      <c r="D32" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="246"/>
+      <c r="F32" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G32" s="250"/>
+      <c r="H32" s="243" t="s">
+        <v>227</v>
+      </c>
+      <c r="I32" s="243" t="s">
+        <v>228</v>
+      </c>
+      <c r="J32" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="246"/>
+      <c r="L32" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="M32" s="250"/>
+    </row>
+    <row r="33" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B33" s="243" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="243" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="250"/>
+      <c r="H33" s="243" t="s">
+        <v>231</v>
+      </c>
+      <c r="I33" s="243" t="s">
+        <v>232</v>
+      </c>
+      <c r="J33" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="250"/>
+    </row>
+    <row r="34" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B34" s="243" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="243" t="s">
+        <v>234</v>
+      </c>
+      <c r="D34" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="246"/>
+      <c r="F34" s="246" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="251"/>
+      <c r="H34" s="243" t="s">
+        <v>235</v>
+      </c>
+      <c r="I34" s="243" t="s">
+        <v>236</v>
+      </c>
+      <c r="J34" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K34" s="246"/>
+      <c r="L34" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34" s="250"/>
+    </row>
+    <row r="35" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B35" s="247" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="236" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="236" t="s">
+      <c r="C35" s="248"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="G35" s="246" t="s">
+        <v>162</v>
+      </c>
+      <c r="H35" s="243" t="s">
+        <v>237</v>
+      </c>
+      <c r="I35" s="243" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M35" s="250"/>
+    </row>
+    <row r="36" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B36" s="243" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="243" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="239" t="s">
+      <c r="E36" s="246"/>
+      <c r="F36" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239" t="s">
+      <c r="G36" s="249" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="240" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="236" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" s="236" t="s">
+      <c r="H36" s="243" t="s">
+        <v>240</v>
+      </c>
+      <c r="I36" s="243" t="s">
+        <v>241</v>
+      </c>
+      <c r="J36" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246" t="s">
         <v>123</v>
       </c>
-      <c r="I6" s="239" t="s">
+      <c r="M36" s="251"/>
+    </row>
+    <row r="37" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B37" s="243" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="243" t="s">
+        <v>243</v>
+      </c>
+      <c r="D37" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G37" s="250"/>
+      <c r="H37" s="247" t="s">
+        <v>244</v>
+      </c>
+      <c r="I37" s="248"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246" t="s">
+        <v>112</v>
+      </c>
+      <c r="L37" s="246" t="s">
+        <v>113</v>
+      </c>
+      <c r="M37" s="246" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" ht="15.95" customHeight="1">
+      <c r="B38" s="243" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" s="243" t="s">
+        <v>246</v>
+      </c>
+      <c r="D38" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="246"/>
+      <c r="F38" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J6" s="239"/>
-      <c r="K6" s="239" t="s">
+      <c r="G38" s="250"/>
+      <c r="H38" s="243" t="s">
+        <v>247</v>
+      </c>
+      <c r="I38" s="243" t="s">
+        <v>248</v>
+      </c>
+      <c r="J38" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K38" s="246"/>
+      <c r="L38" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M38" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="L6" s="240" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="236" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="236" t="s">
+    </row>
+    <row r="39" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B39" s="243" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" s="243" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" s="246" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="239"/>
-      <c r="E7" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" s="241"/>
-      <c r="G7" s="236" t="s">
-        <v>129</v>
-      </c>
-      <c r="H7" s="236" t="s">
-        <v>130</v>
-      </c>
-      <c r="I7" s="239" t="s">
+      <c r="E39" s="246"/>
+      <c r="F39" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="239"/>
-      <c r="K7" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L7" s="241"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A8" s="236" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="236" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="241"/>
-      <c r="G8" s="236" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" s="236" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="239" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L8" s="241"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A9" s="236" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="236" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="241"/>
-      <c r="G9" s="236" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="236" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="239" t="s">
-        <v>140</v>
-      </c>
-      <c r="J9" s="239" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="239" t="s">
-        <v>142</v>
-      </c>
-      <c r="L9" s="241"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A10" s="236" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="236" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="241"/>
-      <c r="G10" s="236" t="s">
-        <v>145</v>
-      </c>
-      <c r="H10" s="236" t="s">
-        <v>146</v>
-      </c>
-      <c r="I10" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L10" s="241"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A11" s="236" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="236" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="241"/>
-      <c r="G11" s="236" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" s="236" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L11" s="241"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="236" t="s">
-        <v>151</v>
-      </c>
-      <c r="B12" s="236" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="239"/>
-      <c r="E12" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F12" s="241"/>
-      <c r="G12" s="236" t="s">
-        <v>153</v>
-      </c>
-      <c r="H12" s="236" t="s">
-        <v>154</v>
-      </c>
-      <c r="I12" s="239" t="s">
+      <c r="G39" s="250"/>
+      <c r="H39" s="243" t="s">
+        <v>251</v>
+      </c>
+      <c r="I39" s="243" t="s">
+        <v>252</v>
+      </c>
+      <c r="J39" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M39" s="250"/>
+    </row>
+    <row r="40" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B40" s="243" t="s">
+        <v>253</v>
+      </c>
+      <c r="C40" s="243" t="s">
+        <v>254</v>
+      </c>
+      <c r="D40" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="239"/>
-      <c r="K12" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L12" s="242"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="236" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="236" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="241"/>
-      <c r="G13" s="233" t="s">
-        <v>157</v>
-      </c>
-      <c r="H13" s="235"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" s="239" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A14" s="236" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="236" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" s="242"/>
-      <c r="G14" s="236" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="236" t="s">
-        <v>161</v>
-      </c>
-      <c r="I14" s="239" t="s">
+      <c r="G40" s="250"/>
+      <c r="H40" s="243" t="s">
+        <v>255</v>
+      </c>
+      <c r="I40" s="243" t="s">
+        <v>256</v>
+      </c>
+      <c r="J40" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M40" s="250"/>
+    </row>
+    <row r="41" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B41" s="243" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="243" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="246"/>
+      <c r="F41" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J14" s="239"/>
-      <c r="K14" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L14" s="240" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="233" t="s">
-        <v>162</v>
-      </c>
-      <c r="B15" s="235"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="239" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="236" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="236" t="s">
-        <v>165</v>
-      </c>
-      <c r="I15" s="239" t="s">
+      <c r="G41" s="250"/>
+      <c r="H41" s="243" t="s">
+        <v>259</v>
+      </c>
+      <c r="I41" s="243" t="s">
+        <v>260</v>
+      </c>
+      <c r="J41" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K41" s="246"/>
+      <c r="L41" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J15" s="239"/>
-      <c r="K15" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L15" s="241"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A16" s="236" t="s">
-        <v>166</v>
-      </c>
-      <c r="B16" s="236" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="239" t="s">
+      <c r="M41" s="250"/>
+    </row>
+    <row r="42" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B42" s="243" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="243" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="246"/>
+      <c r="F42" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="240" t="s">
-        <v>121</v>
-      </c>
-      <c r="G16" s="236" t="s">
-        <v>168</v>
-      </c>
-      <c r="H16" s="236" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" s="239" t="s">
+      <c r="G42" s="250"/>
+      <c r="H42" s="243" t="s">
+        <v>263</v>
+      </c>
+      <c r="I42" s="243" t="s">
+        <v>264</v>
+      </c>
+      <c r="J42" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K42" s="246"/>
+      <c r="L42" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M42" s="250"/>
+    </row>
+    <row r="43" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B43" s="243" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" s="243" t="s">
+        <v>266</v>
+      </c>
+      <c r="D43" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="246"/>
+      <c r="F43" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="J16" s="239"/>
-      <c r="K16" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L16" s="241"/>
-    </row>
-    <row r="17" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A17" s="236" t="s">
-        <v>170</v>
-      </c>
-      <c r="B17" s="236" t="s">
-        <v>171</v>
-      </c>
-      <c r="C17" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="241"/>
-      <c r="G17" s="236" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" s="236" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="239"/>
-      <c r="K17" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L17" s="241"/>
-    </row>
-    <row r="18" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A18" s="236" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18" s="236" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="241"/>
-      <c r="G18" s="236" t="s">
-        <v>176</v>
-      </c>
-      <c r="H18" s="236" t="s">
-        <v>177</v>
-      </c>
-      <c r="I18" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L18" s="241"/>
-    </row>
-    <row r="19" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A19" s="236" t="s">
-        <v>178</v>
-      </c>
-      <c r="B19" s="236" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="239"/>
-      <c r="E19" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="242"/>
-      <c r="G19" s="236" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="236" t="s">
-        <v>181</v>
-      </c>
-      <c r="I19" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="239"/>
-      <c r="K19" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L19" s="241"/>
-    </row>
-    <row r="20" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A20" s="233" t="s">
-        <v>182</v>
-      </c>
-      <c r="B20" s="235"/>
-      <c r="C20" s="239"/>
-      <c r="D20" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="239" t="s">
-        <v>163</v>
-      </c>
-      <c r="G20" s="236" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="236" t="s">
-        <v>184</v>
-      </c>
-      <c r="I20" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20" s="239"/>
-      <c r="K20" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="L20" s="241"/>
-    </row>
-    <row r="21" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A21" s="236" t="s">
-        <v>185</v>
-      </c>
-      <c r="B21" s="236" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="240" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="236" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="236" t="s">
-        <v>188</v>
-      </c>
-      <c r="I21" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="239"/>
-      <c r="K21" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L21" s="241"/>
-    </row>
-    <row r="22" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A22" s="236" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="236" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="239"/>
-      <c r="E22" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F22" s="241"/>
-      <c r="G22" s="236" t="s">
-        <v>190</v>
-      </c>
-      <c r="H22" s="236" t="s">
-        <v>191</v>
-      </c>
-      <c r="I22" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" s="239"/>
-      <c r="K22" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L22" s="241"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A23" s="236" t="s">
-        <v>192</v>
-      </c>
-      <c r="B23" s="236" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="239"/>
-      <c r="E23" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F23" s="241"/>
-      <c r="G23" s="236" t="s">
-        <v>194</v>
-      </c>
-      <c r="H23" s="236" t="s">
-        <v>195</v>
-      </c>
-      <c r="I23" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J23" s="239"/>
-      <c r="K23" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L23" s="241"/>
-    </row>
-    <row r="24" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A24" s="236" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="236" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="239"/>
-      <c r="E24" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="242"/>
-      <c r="G24" s="236" t="s">
-        <v>198</v>
-      </c>
-      <c r="H24" s="236" t="s">
-        <v>199</v>
-      </c>
-      <c r="I24" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J24" s="239"/>
-      <c r="K24" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L24" s="241"/>
-    </row>
-    <row r="25" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A25" s="233" t="s">
-        <v>200</v>
-      </c>
-      <c r="B25" s="235"/>
-      <c r="C25" s="239"/>
-      <c r="D25" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="F25" s="239" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="236" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" s="236" t="s">
-        <v>202</v>
-      </c>
-      <c r="I25" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L25" s="241"/>
-    </row>
-    <row r="26" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A26" s="236" t="s">
-        <v>203</v>
-      </c>
-      <c r="B26" s="236" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="240" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="236" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" s="236" t="s">
-        <v>206</v>
-      </c>
-      <c r="I26" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L26" s="241"/>
-    </row>
-    <row r="27" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A27" s="236" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="236" t="s">
-        <v>208</v>
-      </c>
-      <c r="C27" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="239"/>
-      <c r="E27" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="241"/>
-      <c r="G27" s="236" t="s">
-        <v>209</v>
-      </c>
-      <c r="H27" s="236" t="s">
-        <v>210</v>
-      </c>
-      <c r="I27" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J27" s="239"/>
-      <c r="K27" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L27" s="242"/>
-    </row>
-    <row r="28" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A28" s="236" t="s">
-        <v>211</v>
-      </c>
-      <c r="B28" s="236" t="s">
-        <v>212</v>
-      </c>
-      <c r="C28" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="239"/>
-      <c r="E28" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="241"/>
-      <c r="G28" s="233" t="s">
-        <v>213</v>
-      </c>
-      <c r="H28" s="235"/>
-      <c r="I28" s="239"/>
-      <c r="J28" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="L28" s="239" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A29" s="236" t="s">
-        <v>214</v>
-      </c>
-      <c r="B29" s="236" t="s">
-        <v>215</v>
-      </c>
-      <c r="C29" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="239"/>
-      <c r="E29" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="241"/>
-      <c r="G29" s="236" t="s">
-        <v>216</v>
-      </c>
-      <c r="H29" s="236" t="s">
-        <v>217</v>
-      </c>
-      <c r="I29" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" s="239"/>
-      <c r="K29" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L29" s="240" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A30" s="236" t="s">
-        <v>218</v>
-      </c>
-      <c r="B30" s="236" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="239"/>
-      <c r="E30" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" s="241"/>
-      <c r="G30" s="236" t="s">
-        <v>220</v>
-      </c>
-      <c r="H30" s="236" t="s">
-        <v>221</v>
-      </c>
-      <c r="I30" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J30" s="239"/>
-      <c r="K30" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L30" s="241"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A31" s="236" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="236" t="s">
-        <v>223</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="241"/>
-      <c r="G31" s="236" t="s">
-        <v>224</v>
-      </c>
-      <c r="H31" s="236" t="s">
-        <v>225</v>
-      </c>
-      <c r="I31" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L31" s="241"/>
-    </row>
-    <row r="32" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A32" s="236" t="s">
-        <v>226</v>
-      </c>
-      <c r="B32" s="236" t="s">
-        <v>227</v>
-      </c>
-      <c r="C32" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="239"/>
-      <c r="E32" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="241"/>
-      <c r="G32" s="236" t="s">
-        <v>228</v>
-      </c>
-      <c r="H32" s="236" t="s">
-        <v>229</v>
-      </c>
-      <c r="I32" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J32" s="239"/>
-      <c r="K32" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="L32" s="241"/>
-    </row>
-    <row r="33" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A33" s="236" t="s">
-        <v>230</v>
-      </c>
-      <c r="B33" s="236" t="s">
-        <v>231</v>
-      </c>
-      <c r="C33" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="241"/>
-      <c r="G33" s="236" t="s">
-        <v>232</v>
-      </c>
-      <c r="H33" s="236" t="s">
-        <v>233</v>
-      </c>
-      <c r="I33" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L33" s="241"/>
-    </row>
-    <row r="34" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A34" s="236" t="s">
-        <v>234</v>
-      </c>
-      <c r="B34" s="236" t="s">
-        <v>235</v>
-      </c>
-      <c r="C34" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="239"/>
-      <c r="E34" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="242"/>
-      <c r="G34" s="236" t="s">
-        <v>236</v>
-      </c>
-      <c r="H34" s="236" t="s">
-        <v>237</v>
-      </c>
-      <c r="I34" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J34" s="239"/>
-      <c r="K34" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L34" s="241"/>
-    </row>
-    <row r="35" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A35" s="233" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="235"/>
-      <c r="C35" s="239"/>
-      <c r="D35" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="F35" s="239" t="s">
-        <v>163</v>
-      </c>
-      <c r="G35" s="236" t="s">
-        <v>238</v>
-      </c>
-      <c r="H35" s="236" t="s">
-        <v>191</v>
-      </c>
-      <c r="I35" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J35" s="239"/>
-      <c r="K35" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L35" s="241"/>
-    </row>
-    <row r="36" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A36" s="236" t="s">
-        <v>239</v>
-      </c>
-      <c r="B36" s="236" t="s">
-        <v>240</v>
-      </c>
-      <c r="C36" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="239"/>
-      <c r="E36" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="240" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="236" t="s">
-        <v>241</v>
-      </c>
-      <c r="H36" s="236" t="s">
-        <v>242</v>
-      </c>
-      <c r="I36" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J36" s="239"/>
-      <c r="K36" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L36" s="242"/>
-    </row>
-    <row r="37" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A37" s="236" t="s">
-        <v>243</v>
-      </c>
-      <c r="B37" s="236" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="239"/>
-      <c r="E37" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="241"/>
-      <c r="G37" s="233" t="s">
-        <v>245</v>
-      </c>
-      <c r="H37" s="235"/>
-      <c r="I37" s="239"/>
-      <c r="J37" s="239" t="s">
-        <v>113</v>
-      </c>
-      <c r="K37" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="L37" s="239" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="15.95" customHeight="1">
-      <c r="A38" s="236" t="s">
-        <v>246</v>
-      </c>
-      <c r="B38" s="236" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="239"/>
-      <c r="E38" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F38" s="241"/>
-      <c r="G38" s="236" t="s">
-        <v>248</v>
-      </c>
-      <c r="H38" s="236" t="s">
-        <v>249</v>
-      </c>
-      <c r="I38" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J38" s="239"/>
-      <c r="K38" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L38" s="240" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A39" s="236" t="s">
-        <v>250</v>
-      </c>
-      <c r="B39" s="236" t="s">
-        <v>251</v>
-      </c>
-      <c r="C39" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="239"/>
-      <c r="E39" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="241"/>
-      <c r="G39" s="236" t="s">
-        <v>252</v>
-      </c>
-      <c r="H39" s="236" t="s">
-        <v>253</v>
-      </c>
-      <c r="I39" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J39" s="239"/>
-      <c r="K39" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L39" s="241"/>
-    </row>
-    <row r="40" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A40" s="236" t="s">
-        <v>254</v>
-      </c>
-      <c r="B40" s="236" t="s">
-        <v>255</v>
-      </c>
-      <c r="C40" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F40" s="241"/>
-      <c r="G40" s="236" t="s">
-        <v>256</v>
-      </c>
-      <c r="H40" s="236" t="s">
-        <v>257</v>
-      </c>
-      <c r="I40" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L40" s="241"/>
-    </row>
-    <row r="41" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A41" s="236" t="s">
-        <v>258</v>
-      </c>
-      <c r="B41" s="236" t="s">
-        <v>259</v>
-      </c>
-      <c r="C41" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="239"/>
-      <c r="E41" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F41" s="241"/>
-      <c r="G41" s="236" t="s">
-        <v>260</v>
-      </c>
-      <c r="H41" s="236" t="s">
-        <v>261</v>
-      </c>
-      <c r="I41" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J41" s="239"/>
-      <c r="K41" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="L41" s="241"/>
-    </row>
-    <row r="42" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A42" s="236" t="s">
-        <v>262</v>
-      </c>
-      <c r="B42" s="236" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="239"/>
-      <c r="E42" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F42" s="241"/>
-      <c r="G42" s="236" t="s">
-        <v>264</v>
-      </c>
-      <c r="H42" s="236" t="s">
-        <v>265</v>
-      </c>
-      <c r="I42" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J42" s="239"/>
-      <c r="K42" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L42" s="241"/>
-    </row>
-    <row r="43" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A43" s="236" t="s">
-        <v>266</v>
-      </c>
-      <c r="B43" s="236" t="s">
+      <c r="G43" s="250"/>
+      <c r="H43" s="243" t="s">
         <v>267</v>
       </c>
-      <c r="C43" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="239"/>
-      <c r="E43" s="239" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="241"/>
-      <c r="G43" s="236" t="s">
+      <c r="I43" s="243" t="s">
         <v>268</v>
       </c>
-      <c r="H43" s="236" t="s">
+      <c r="J43" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="K43" s="246"/>
+      <c r="L43" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M43" s="250"/>
+    </row>
+    <row r="44" spans="2:13" ht="17.100000000000001" customHeight="1">
+      <c r="B44" s="243" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="J43" s="239"/>
-      <c r="K43" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L43" s="241"/>
-    </row>
-    <row r="44" spans="1:12" ht="17.100000000000001" customHeight="1">
-      <c r="A44" s="236" t="s">
+      <c r="C44" s="243" t="s">
         <v>270</v>
       </c>
-      <c r="B44" s="236" t="s">
+      <c r="D44" s="246" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="239" t="s">
+      <c r="E44" s="246"/>
+      <c r="F44" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="251"/>
+      <c r="H44" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="239"/>
-      <c r="E44" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="242"/>
-      <c r="G44" s="236" t="s">
+      <c r="I44" s="243" t="s">
         <v>273</v>
       </c>
-      <c r="H44" s="236" t="s">
+      <c r="J44" s="246" t="s">
+        <v>127</v>
+      </c>
+      <c r="K44" s="246"/>
+      <c r="L44" s="246" t="s">
+        <v>123</v>
+      </c>
+      <c r="M44" s="251"/>
+    </row>
+    <row r="45" spans="2:13" ht="21.95" customHeight="1">
+      <c r="B45" s="252" t="s">
         <v>274</v>
       </c>
-      <c r="I44" s="239" t="s">
-        <v>128</v>
-      </c>
-      <c r="J44" s="239"/>
-      <c r="K44" s="239" t="s">
-        <v>124</v>
-      </c>
-      <c r="L44" s="242"/>
-    </row>
-    <row r="45" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A45" s="243" t="s">
-        <v>275</v>
-      </c>
-      <c r="B45" s="244"/>
-      <c r="C45" s="244"/>
-      <c r="D45" s="244"/>
-      <c r="E45" s="244"/>
-      <c r="F45" s="244"/>
-      <c r="G45" s="244"/>
-      <c r="H45" s="244"/>
-      <c r="I45" s="244"/>
-      <c r="J45" s="244"/>
-      <c r="K45" s="244"/>
-      <c r="L45" s="245"/>
-    </row>
-    <row r="46" spans="1:12" ht="23.1" customHeight="1">
-      <c r="A46" s="246"/>
-      <c r="B46" s="247"/>
-      <c r="C46" s="247"/>
-      <c r="D46" s="247"/>
-      <c r="E46" s="247"/>
-      <c r="F46" s="247"/>
-      <c r="G46" s="247"/>
-      <c r="H46" s="247"/>
-      <c r="I46" s="247"/>
-      <c r="J46" s="247"/>
-      <c r="K46" s="247"/>
-      <c r="L46" s="248"/>
+      <c r="C45" s="253"/>
+      <c r="D45" s="253"/>
+      <c r="E45" s="253"/>
+      <c r="F45" s="253"/>
+      <c r="G45" s="253"/>
+      <c r="H45" s="253"/>
+      <c r="I45" s="253"/>
+      <c r="J45" s="253"/>
+      <c r="K45" s="253"/>
+      <c r="L45" s="253"/>
+      <c r="M45" s="254"/>
+    </row>
+    <row r="46" spans="2:13" ht="23.1" customHeight="1">
+      <c r="B46" s="255"/>
+      <c r="C46" s="256"/>
+      <c r="D46" s="256"/>
+      <c r="E46" s="256"/>
+      <c r="F46" s="256"/>
+      <c r="G46" s="256"/>
+      <c r="H46" s="256"/>
+      <c r="I46" s="256"/>
+      <c r="J46" s="256"/>
+      <c r="K46" s="256"/>
+      <c r="L46" s="256"/>
+      <c r="M46" s="257"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A45:L46"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="F26:F34"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="L29:L36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F36:F44"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="L38:L44"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F6:F14"/>
-    <mergeCell ref="L6:L12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="L14:L27"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F16:F19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
+  <mergeCells count="27">
+    <mergeCell ref="B45:M46"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="G26:G34"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="M29:M36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="M38:M44"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="G6:G14"/>
+    <mergeCell ref="M6:M12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="M14:M27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCD82E1-8FE7-42BC-9C2E-21357129193B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8729051F-D93D-4071-A906-00E9144AF7AD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10000,748 +10131,748 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B1" s="249"/>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
-      <c r="G1" s="249"/>
-      <c r="H1" s="249"/>
-      <c r="I1" s="249"/>
-      <c r="J1" s="249"/>
-      <c r="K1" s="249"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
     </row>
     <row r="2" spans="2:11">
-      <c r="B2" s="249"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
     </row>
     <row r="3" spans="2:11" ht="27">
-      <c r="B3" s="250" t="s">
+      <c r="B3" s="259" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="251" t="s">
+      <c r="D3" s="260"/>
+      <c r="E3" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="250" t="s">
+      <c r="F3" s="261" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="253" t="s">
+      <c r="G3" s="233" t="s">
         <v>279</v>
       </c>
-      <c r="G3" s="254" t="s">
+      <c r="H3" s="234"/>
+      <c r="I3" s="262" t="s">
+        <v>364</v>
+      </c>
+      <c r="J3" s="263"/>
+      <c r="K3" s="264"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="259" t="s">
         <v>280</v>
       </c>
-      <c r="H3" s="255"/>
-      <c r="I3" s="256" t="s">
+      <c r="C4" s="262" t="s">
         <v>281</v>
       </c>
-      <c r="J3" s="257"/>
-      <c r="K3" s="258"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="250" t="s">
+      <c r="D4" s="264"/>
+      <c r="E4" s="259" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="256" t="s">
+      <c r="F4" s="261" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="250" t="s">
+      <c r="G4" s="233" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="253" t="s">
+      <c r="H4" s="234"/>
+      <c r="I4" s="240" t="s">
         <v>285</v>
       </c>
-      <c r="G4" s="254" t="s">
+      <c r="J4" s="241"/>
+      <c r="K4" s="260"/>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="259" t="s">
         <v>286</v>
       </c>
-      <c r="H4" s="255"/>
-      <c r="I4" s="251" t="s">
+      <c r="C5" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="J4" s="259"/>
-      <c r="K4" s="252"/>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="250" t="s">
+      <c r="D5" s="260"/>
+      <c r="E5" s="259" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="251" t="s">
+      <c r="F5" s="261" t="s">
         <v>289</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="250" t="s">
+      <c r="G5" s="233" t="s">
         <v>290</v>
       </c>
-      <c r="F5" s="253" t="s">
+      <c r="H5" s="234"/>
+      <c r="I5" s="240" t="s">
         <v>291</v>
       </c>
-      <c r="G5" s="254" t="s">
+      <c r="J5" s="260"/>
+      <c r="K5" s="261" t="s">
         <v>292</v>
       </c>
-      <c r="H5" s="255"/>
-      <c r="I5" s="251" t="s">
+    </row>
+    <row r="6" spans="2:11" ht="26.25" customHeight="1">
+      <c r="B6" s="259" t="s">
         <v>293</v>
       </c>
-      <c r="J5" s="252"/>
-      <c r="K5" s="253" t="s">
+      <c r="C6" s="262" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B6" s="250" t="s">
+      <c r="D6" s="264"/>
+      <c r="E6" s="259" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="256" t="s">
+      <c r="F6" s="261" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="258"/>
-      <c r="E6" s="250" t="s">
+      <c r="G6" s="233" t="s">
         <v>297</v>
       </c>
-      <c r="F6" s="253" t="s">
+      <c r="H6" s="234"/>
+      <c r="I6" s="235" t="s">
         <v>298</v>
       </c>
-      <c r="G6" s="254" t="s">
+      <c r="J6" s="241"/>
+      <c r="K6" s="260"/>
+    </row>
+    <row r="7" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B7" s="259" t="s">
         <v>299</v>
       </c>
-      <c r="H6" s="255"/>
-      <c r="I6" s="260" t="s">
+      <c r="C7" s="265" t="s">
+        <v>365</v>
+      </c>
+      <c r="D7" s="266"/>
+      <c r="E7" s="259" t="s">
         <v>300</v>
       </c>
-      <c r="J6" s="259"/>
-      <c r="K6" s="252"/>
-    </row>
-    <row r="7" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B7" s="250" t="s">
+      <c r="F7" s="267" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="260" t="s">
+      <c r="G7" s="233" t="s">
         <v>302</v>
       </c>
-      <c r="D7" s="252"/>
-      <c r="E7" s="250" t="s">
+      <c r="H7" s="234"/>
+      <c r="I7" s="240" t="s">
         <v>303</v>
       </c>
-      <c r="F7" s="261" t="s">
+      <c r="J7" s="241"/>
+      <c r="K7" s="260"/>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="268"/>
+      <c r="C8" s="269"/>
+      <c r="D8" s="269"/>
+      <c r="E8" s="269"/>
+      <c r="F8" s="269"/>
+      <c r="G8" s="269"/>
+      <c r="H8" s="269"/>
+      <c r="I8" s="269"/>
+      <c r="J8" s="269"/>
+      <c r="K8" s="270"/>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="259" t="s">
         <v>304</v>
       </c>
-      <c r="G7" s="254" t="s">
+      <c r="C9" s="233" t="s">
         <v>305</v>
       </c>
-      <c r="H7" s="255"/>
-      <c r="I7" s="251" t="s">
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="259" t="s">
         <v>306</v>
       </c>
-      <c r="J7" s="259"/>
-      <c r="K7" s="252"/>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="262"/>
-      <c r="C8" s="263"/>
-      <c r="D8" s="263"/>
-      <c r="E8" s="263"/>
-      <c r="F8" s="263"/>
-      <c r="G8" s="263"/>
-      <c r="H8" s="263"/>
-      <c r="I8" s="263"/>
-      <c r="J8" s="263"/>
-      <c r="K8" s="264"/>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="250" t="s">
+      <c r="J9" s="233" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="254" t="s">
+      <c r="K9" s="234"/>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="268" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="265"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="250" t="s">
+      <c r="C10" s="269"/>
+      <c r="D10" s="269"/>
+      <c r="E10" s="269"/>
+      <c r="F10" s="269"/>
+      <c r="G10" s="269"/>
+      <c r="H10" s="269"/>
+      <c r="I10" s="269"/>
+      <c r="J10" s="269"/>
+      <c r="K10" s="270"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="272" t="s">
         <v>309</v>
       </c>
-      <c r="J9" s="254" t="s">
+      <c r="C11" s="268" t="s">
         <v>310</v>
       </c>
-      <c r="K9" s="255"/>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="262" t="s">
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="270"/>
+      <c r="I11" s="261" t="s">
         <v>311</v>
       </c>
-      <c r="C10" s="263"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="263"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="263"/>
-      <c r="H10" s="263"/>
-      <c r="I10" s="263"/>
-      <c r="J10" s="263"/>
-      <c r="K10" s="264"/>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="266" t="s">
+      <c r="J11" s="268"/>
+      <c r="K11" s="270"/>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="273"/>
+      <c r="C12" s="268" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="262" t="s">
+      <c r="D12" s="269"/>
+      <c r="E12" s="269"/>
+      <c r="F12" s="269"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="270"/>
+      <c r="I12" s="261" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="E11" s="263"/>
-      <c r="F11" s="263"/>
-      <c r="G11" s="263"/>
-      <c r="H11" s="264"/>
-      <c r="I11" s="253" t="s">
+      <c r="J12" s="268"/>
+      <c r="K12" s="270"/>
+    </row>
+    <row r="13" spans="2:11" ht="25.5" customHeight="1">
+      <c r="B13" s="274"/>
+      <c r="C13" s="268" t="s">
         <v>314</v>
       </c>
-      <c r="J11" s="262"/>
-      <c r="K11" s="264"/>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="267"/>
-      <c r="C12" s="262" t="s">
+      <c r="D13" s="269"/>
+      <c r="E13" s="269"/>
+      <c r="F13" s="269"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="270"/>
+      <c r="I13" s="261" t="s">
+        <v>313</v>
+      </c>
+      <c r="J13" s="268"/>
+      <c r="K13" s="270"/>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="268" t="s">
         <v>315</v>
       </c>
-      <c r="D12" s="263"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="263"/>
-      <c r="G12" s="263"/>
-      <c r="H12" s="264"/>
-      <c r="I12" s="253" t="s">
+      <c r="C14" s="269"/>
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="269"/>
+      <c r="I14" s="269"/>
+      <c r="J14" s="269"/>
+      <c r="K14" s="270"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="272" t="s">
         <v>316</v>
       </c>
-      <c r="J12" s="262"/>
-      <c r="K12" s="264"/>
-    </row>
-    <row r="13" spans="2:11" ht="25.5" customHeight="1">
-      <c r="B13" s="268"/>
-      <c r="C13" s="262" t="s">
+      <c r="C15" s="268" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="E13" s="263"/>
-      <c r="F13" s="263"/>
-      <c r="G13" s="263"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="253" t="s">
-        <v>316</v>
-      </c>
-      <c r="J13" s="262"/>
-      <c r="K13" s="264"/>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="262" t="s">
+      <c r="D15" s="269"/>
+      <c r="E15" s="269"/>
+      <c r="F15" s="269"/>
+      <c r="G15" s="269"/>
+      <c r="H15" s="270"/>
+      <c r="I15" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J15" s="276"/>
+      <c r="K15" s="277"/>
+    </row>
+    <row r="16" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B16" s="274"/>
+      <c r="C16" s="268" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="263"/>
-      <c r="D14" s="263"/>
-      <c r="E14" s="263"/>
-      <c r="F14" s="263"/>
-      <c r="G14" s="263"/>
-      <c r="H14" s="263"/>
-      <c r="I14" s="263"/>
-      <c r="J14" s="263"/>
-      <c r="K14" s="264"/>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="266" t="s">
+      <c r="D16" s="269"/>
+      <c r="E16" s="269"/>
+      <c r="F16" s="269"/>
+      <c r="G16" s="269"/>
+      <c r="H16" s="270"/>
+      <c r="I16" s="278"/>
+      <c r="J16" s="279"/>
+      <c r="K16" s="280"/>
+    </row>
+    <row r="17" spans="2:11" ht="18" customHeight="1">
+      <c r="B17" s="272" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="262" t="s">
+      <c r="C17" s="268" t="s">
         <v>320</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="E15" s="263"/>
-      <c r="F15" s="263"/>
-      <c r="G15" s="263"/>
-      <c r="H15" s="264"/>
-      <c r="I15" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J15" s="270"/>
-      <c r="K15" s="271"/>
-    </row>
-    <row r="16" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B16" s="268"/>
-      <c r="C16" s="262" t="s">
+      <c r="D17" s="269"/>
+      <c r="E17" s="269"/>
+      <c r="F17" s="269"/>
+      <c r="G17" s="269"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J17" s="276"/>
+      <c r="K17" s="277"/>
+    </row>
+    <row r="18" spans="2:11" ht="27" customHeight="1">
+      <c r="B18" s="273"/>
+      <c r="C18" s="268" t="s">
         <v>321</v>
       </c>
-      <c r="D16" s="263"/>
-      <c r="E16" s="263"/>
-      <c r="F16" s="263"/>
-      <c r="G16" s="263"/>
-      <c r="H16" s="264"/>
-      <c r="I16" s="272"/>
-      <c r="J16" s="273"/>
-      <c r="K16" s="274"/>
-    </row>
-    <row r="17" spans="2:11" ht="18" customHeight="1">
-      <c r="B17" s="266" t="s">
+      <c r="D18" s="269"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="269"/>
+      <c r="G18" s="269"/>
+      <c r="H18" s="270"/>
+      <c r="I18" s="281"/>
+      <c r="J18" s="282"/>
+      <c r="K18" s="283"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="273"/>
+      <c r="C19" s="268" t="s">
         <v>322</v>
       </c>
-      <c r="C17" s="262" t="s">
+      <c r="D19" s="269"/>
+      <c r="E19" s="269"/>
+      <c r="F19" s="269"/>
+      <c r="G19" s="269"/>
+      <c r="H19" s="270"/>
+      <c r="I19" s="281"/>
+      <c r="J19" s="282"/>
+      <c r="K19" s="283"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="274"/>
+      <c r="C20" s="268" t="s">
         <v>323</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="E17" s="263"/>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J17" s="270"/>
-      <c r="K17" s="271"/>
-    </row>
-    <row r="18" spans="2:11" ht="27" customHeight="1">
-      <c r="B18" s="267"/>
-      <c r="C18" s="262" t="s">
+      <c r="D20" s="269"/>
+      <c r="E20" s="269"/>
+      <c r="F20" s="269"/>
+      <c r="G20" s="269"/>
+      <c r="H20" s="270"/>
+      <c r="I20" s="278"/>
+      <c r="J20" s="279"/>
+      <c r="K20" s="280"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="268" t="s">
         <v>324</v>
       </c>
-      <c r="D18" s="263"/>
-      <c r="E18" s="263"/>
-      <c r="F18" s="263"/>
-      <c r="G18" s="263"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="275"/>
-      <c r="J18" s="276"/>
-      <c r="K18" s="277"/>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="267"/>
-      <c r="C19" s="262" t="s">
+      <c r="C21" s="269"/>
+      <c r="D21" s="269"/>
+      <c r="E21" s="269"/>
+      <c r="F21" s="269"/>
+      <c r="G21" s="269"/>
+      <c r="H21" s="269"/>
+      <c r="I21" s="269"/>
+      <c r="J21" s="269"/>
+      <c r="K21" s="270"/>
+    </row>
+    <row r="22" spans="2:11" ht="18" customHeight="1">
+      <c r="B22" s="272" t="s">
         <v>325</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="E19" s="263"/>
-      <c r="F19" s="263"/>
-      <c r="G19" s="263"/>
-      <c r="H19" s="264"/>
-      <c r="I19" s="275"/>
-      <c r="J19" s="276"/>
-      <c r="K19" s="277"/>
-    </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="268"/>
-      <c r="C20" s="262" t="s">
+      <c r="C22" s="268" t="s">
         <v>326</v>
       </c>
-      <c r="D20" s="263"/>
-      <c r="E20" s="263"/>
-      <c r="F20" s="263"/>
-      <c r="G20" s="263"/>
-      <c r="H20" s="264"/>
-      <c r="I20" s="272"/>
-      <c r="J20" s="273"/>
-      <c r="K20" s="274"/>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="262" t="s">
+      <c r="D22" s="269"/>
+      <c r="E22" s="269"/>
+      <c r="F22" s="269"/>
+      <c r="G22" s="269"/>
+      <c r="H22" s="270"/>
+      <c r="I22" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J22" s="276"/>
+      <c r="K22" s="277"/>
+    </row>
+    <row r="23" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B23" s="274"/>
+      <c r="C23" s="268" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="263"/>
-      <c r="D21" s="263"/>
-      <c r="E21" s="263"/>
-      <c r="F21" s="263"/>
-      <c r="G21" s="263"/>
-      <c r="H21" s="263"/>
-      <c r="I21" s="263"/>
-      <c r="J21" s="263"/>
-      <c r="K21" s="264"/>
-    </row>
-    <row r="22" spans="2:11" ht="18" customHeight="1">
-      <c r="B22" s="266" t="s">
+      <c r="D23" s="269"/>
+      <c r="E23" s="269"/>
+      <c r="F23" s="269"/>
+      <c r="G23" s="269"/>
+      <c r="H23" s="270"/>
+      <c r="I23" s="278"/>
+      <c r="J23" s="279"/>
+      <c r="K23" s="280"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="268" t="s">
         <v>328</v>
       </c>
-      <c r="C22" s="262" t="s">
+      <c r="C24" s="269"/>
+      <c r="D24" s="269"/>
+      <c r="E24" s="269"/>
+      <c r="F24" s="269"/>
+      <c r="G24" s="269"/>
+      <c r="H24" s="269"/>
+      <c r="I24" s="269"/>
+      <c r="J24" s="269"/>
+      <c r="K24" s="270"/>
+    </row>
+    <row r="25" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B25" s="272" t="s">
         <v>329</v>
       </c>
-      <c r="D22" s="263"/>
-      <c r="E22" s="263"/>
-      <c r="F22" s="263"/>
-      <c r="G22" s="263"/>
-      <c r="H22" s="264"/>
-      <c r="I22" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J22" s="270"/>
-      <c r="K22" s="271"/>
-    </row>
-    <row r="23" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B23" s="268"/>
-      <c r="C23" s="262" t="s">
+      <c r="C25" s="268" t="s">
         <v>330</v>
       </c>
-      <c r="D23" s="263"/>
-      <c r="E23" s="263"/>
-      <c r="F23" s="263"/>
-      <c r="G23" s="263"/>
-      <c r="H23" s="264"/>
-      <c r="I23" s="272"/>
-      <c r="J23" s="273"/>
-      <c r="K23" s="274"/>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="262" t="s">
+      <c r="D25" s="269"/>
+      <c r="E25" s="269"/>
+      <c r="F25" s="269"/>
+      <c r="G25" s="269"/>
+      <c r="H25" s="270"/>
+      <c r="I25" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J25" s="276"/>
+      <c r="K25" s="277"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="274"/>
+      <c r="C26" s="268" t="s">
         <v>331</v>
       </c>
-      <c r="C24" s="263"/>
-      <c r="D24" s="263"/>
-      <c r="E24" s="263"/>
-      <c r="F24" s="263"/>
-      <c r="G24" s="263"/>
-      <c r="H24" s="263"/>
-      <c r="I24" s="263"/>
-      <c r="J24" s="263"/>
-      <c r="K24" s="264"/>
-    </row>
-    <row r="25" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B25" s="266" t="s">
+      <c r="D26" s="269"/>
+      <c r="E26" s="269"/>
+      <c r="F26" s="269"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="270"/>
+      <c r="I26" s="278"/>
+      <c r="J26" s="279"/>
+      <c r="K26" s="280"/>
+    </row>
+    <row r="27" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B27" s="284" t="s">
         <v>332</v>
       </c>
-      <c r="C25" s="262" t="s">
+      <c r="C27" s="268" t="s">
         <v>333</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="E25" s="263"/>
-      <c r="F25" s="263"/>
-      <c r="G25" s="263"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J25" s="270"/>
-      <c r="K25" s="271"/>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="268"/>
-      <c r="C26" s="262" t="s">
+      <c r="D27" s="269"/>
+      <c r="E27" s="269"/>
+      <c r="F27" s="269"/>
+      <c r="G27" s="269"/>
+      <c r="H27" s="270"/>
+      <c r="I27" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J27" s="268"/>
+      <c r="K27" s="270"/>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="268" t="s">
         <v>334</v>
       </c>
-      <c r="D26" s="263"/>
-      <c r="E26" s="263"/>
-      <c r="F26" s="263"/>
-      <c r="G26" s="263"/>
-      <c r="H26" s="264"/>
-      <c r="I26" s="272"/>
-      <c r="J26" s="273"/>
-      <c r="K26" s="274"/>
-    </row>
-    <row r="27" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B27" s="278" t="s">
+      <c r="C28" s="269"/>
+      <c r="D28" s="269"/>
+      <c r="E28" s="269"/>
+      <c r="F28" s="269"/>
+      <c r="G28" s="269"/>
+      <c r="H28" s="269"/>
+      <c r="I28" s="269"/>
+      <c r="J28" s="269"/>
+      <c r="K28" s="270"/>
+    </row>
+    <row r="29" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B29" s="272" t="s">
         <v>335</v>
       </c>
-      <c r="C27" s="262" t="s">
+      <c r="C29" s="268" t="s">
         <v>336</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="E27" s="263"/>
-      <c r="F27" s="263"/>
-      <c r="G27" s="263"/>
-      <c r="H27" s="264"/>
-      <c r="I27" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J27" s="262"/>
-      <c r="K27" s="264"/>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="262" t="s">
+      <c r="D29" s="269"/>
+      <c r="E29" s="269"/>
+      <c r="F29" s="269"/>
+      <c r="G29" s="269"/>
+      <c r="H29" s="270"/>
+      <c r="I29" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J29" s="276"/>
+      <c r="K29" s="277"/>
+    </row>
+    <row r="30" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B30" s="274"/>
+      <c r="C30" s="268" t="s">
         <v>337</v>
       </c>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
-      <c r="F28" s="263"/>
-      <c r="G28" s="263"/>
-      <c r="H28" s="263"/>
-      <c r="I28" s="263"/>
-      <c r="J28" s="263"/>
-      <c r="K28" s="264"/>
-    </row>
-    <row r="29" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B29" s="266" t="s">
+      <c r="D30" s="269"/>
+      <c r="E30" s="269"/>
+      <c r="F30" s="269"/>
+      <c r="G30" s="269"/>
+      <c r="H30" s="270"/>
+      <c r="I30" s="278"/>
+      <c r="J30" s="279"/>
+      <c r="K30" s="280"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="268" t="s">
         <v>338</v>
       </c>
-      <c r="C29" s="262" t="s">
+      <c r="C31" s="269"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="270"/>
+    </row>
+    <row r="32" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B32" s="272" t="s">
         <v>339</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="E29" s="263"/>
-      <c r="F29" s="263"/>
-      <c r="G29" s="263"/>
-      <c r="H29" s="264"/>
-      <c r="I29" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J29" s="270"/>
-      <c r="K29" s="271"/>
-    </row>
-    <row r="30" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B30" s="268"/>
-      <c r="C30" s="262" t="s">
+      <c r="C32" s="268" t="s">
         <v>340</v>
       </c>
-      <c r="D30" s="263"/>
-      <c r="E30" s="263"/>
-      <c r="F30" s="263"/>
-      <c r="G30" s="263"/>
-      <c r="H30" s="264"/>
-      <c r="I30" s="272"/>
-      <c r="J30" s="273"/>
-      <c r="K30" s="274"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="262" t="s">
+      <c r="D32" s="269"/>
+      <c r="E32" s="269"/>
+      <c r="F32" s="269"/>
+      <c r="G32" s="269"/>
+      <c r="H32" s="270"/>
+      <c r="I32" s="275" t="s">
+        <v>311</v>
+      </c>
+      <c r="J32" s="276"/>
+      <c r="K32" s="277"/>
+    </row>
+    <row r="33" spans="2:11" ht="18" customHeight="1">
+      <c r="B33" s="273"/>
+      <c r="C33" s="268" t="s">
         <v>341</v>
       </c>
-      <c r="C31" s="263"/>
-      <c r="D31" s="263"/>
-      <c r="E31" s="263"/>
-      <c r="F31" s="263"/>
-      <c r="G31" s="263"/>
-      <c r="H31" s="263"/>
-      <c r="I31" s="263"/>
-      <c r="J31" s="263"/>
-      <c r="K31" s="264"/>
-    </row>
-    <row r="32" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B32" s="266" t="s">
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="269"/>
+      <c r="G33" s="269"/>
+      <c r="H33" s="270"/>
+      <c r="I33" s="281"/>
+      <c r="J33" s="282"/>
+      <c r="K33" s="283"/>
+    </row>
+    <row r="34" spans="2:11" ht="18" customHeight="1">
+      <c r="B34" s="274"/>
+      <c r="C34" s="268" t="s">
         <v>342</v>
       </c>
-      <c r="C32" s="262" t="s">
+      <c r="D34" s="269"/>
+      <c r="E34" s="269"/>
+      <c r="F34" s="269"/>
+      <c r="G34" s="269"/>
+      <c r="H34" s="270"/>
+      <c r="I34" s="278"/>
+      <c r="J34" s="279"/>
+      <c r="K34" s="280"/>
+    </row>
+    <row r="35" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B35" s="268" t="s">
         <v>343</v>
       </c>
-      <c r="D32" s="263"/>
-      <c r="E32" s="263"/>
-      <c r="F32" s="263"/>
-      <c r="G32" s="263"/>
-      <c r="H32" s="264"/>
-      <c r="I32" s="269" t="s">
-        <v>314</v>
-      </c>
-      <c r="J32" s="270"/>
-      <c r="K32" s="271"/>
-    </row>
-    <row r="33" spans="2:11" ht="18" customHeight="1">
-      <c r="B33" s="267"/>
-      <c r="C33" s="262" t="s">
+      <c r="C35" s="269"/>
+      <c r="D35" s="269"/>
+      <c r="E35" s="269"/>
+      <c r="F35" s="269"/>
+      <c r="G35" s="269"/>
+      <c r="H35" s="269"/>
+      <c r="I35" s="269"/>
+      <c r="J35" s="269"/>
+      <c r="K35" s="270"/>
+    </row>
+    <row r="36" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B36" s="284" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="E33" s="263"/>
-      <c r="F33" s="263"/>
-      <c r="G33" s="263"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="275"/>
-      <c r="J33" s="276"/>
-      <c r="K33" s="277"/>
-    </row>
-    <row r="34" spans="2:11" ht="18" customHeight="1">
-      <c r="B34" s="268"/>
-      <c r="C34" s="262" t="s">
+      <c r="C36" s="268" t="s">
         <v>345</v>
       </c>
-      <c r="D34" s="263"/>
-      <c r="E34" s="263"/>
-      <c r="F34" s="263"/>
-      <c r="G34" s="263"/>
-      <c r="H34" s="264"/>
-      <c r="I34" s="272"/>
-      <c r="J34" s="273"/>
-      <c r="K34" s="274"/>
-    </row>
-    <row r="35" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B35" s="262" t="s">
+      <c r="D36" s="269"/>
+      <c r="E36" s="269"/>
+      <c r="F36" s="269"/>
+      <c r="G36" s="269"/>
+      <c r="H36" s="270"/>
+      <c r="I36" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J36" s="268"/>
+      <c r="K36" s="270"/>
+    </row>
+    <row r="37" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B37" s="284" t="s">
         <v>346</v>
       </c>
-      <c r="C35" s="263"/>
-      <c r="D35" s="263"/>
-      <c r="E35" s="263"/>
-      <c r="F35" s="263"/>
-      <c r="G35" s="263"/>
-      <c r="H35" s="263"/>
-      <c r="I35" s="263"/>
-      <c r="J35" s="263"/>
-      <c r="K35" s="264"/>
-    </row>
-    <row r="36" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B36" s="278" t="s">
+      <c r="C37" s="268" t="s">
         <v>347</v>
       </c>
-      <c r="C36" s="262" t="s">
+      <c r="D37" s="269"/>
+      <c r="E37" s="269"/>
+      <c r="F37" s="269"/>
+      <c r="G37" s="269"/>
+      <c r="H37" s="270"/>
+      <c r="I37" s="261" t="s">
+        <v>313</v>
+      </c>
+      <c r="J37" s="268"/>
+      <c r="K37" s="270"/>
+    </row>
+    <row r="38" spans="2:11" ht="18" customHeight="1">
+      <c r="B38" s="285" t="s">
         <v>348</v>
       </c>
-      <c r="D36" s="263"/>
-      <c r="E36" s="263"/>
-      <c r="F36" s="263"/>
-      <c r="G36" s="263"/>
-      <c r="H36" s="264"/>
-      <c r="I36" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J36" s="262"/>
-      <c r="K36" s="264"/>
-    </row>
-    <row r="37" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B37" s="278" t="s">
+      <c r="C38" s="268" t="s">
         <v>349</v>
       </c>
-      <c r="C37" s="262" t="s">
+      <c r="D38" s="269"/>
+      <c r="E38" s="269"/>
+      <c r="F38" s="269"/>
+      <c r="G38" s="269"/>
+      <c r="H38" s="270"/>
+      <c r="I38" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J38" s="268"/>
+      <c r="K38" s="270"/>
+    </row>
+    <row r="39" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B39" s="268" t="s">
         <v>350</v>
       </c>
-      <c r="D37" s="263"/>
-      <c r="E37" s="263"/>
-      <c r="F37" s="263"/>
-      <c r="G37" s="263"/>
-      <c r="H37" s="264"/>
-      <c r="I37" s="253" t="s">
-        <v>316</v>
-      </c>
-      <c r="J37" s="262"/>
-      <c r="K37" s="264"/>
-    </row>
-    <row r="38" spans="2:11" ht="18" customHeight="1">
-      <c r="B38" s="279" t="s">
+      <c r="C39" s="269"/>
+      <c r="D39" s="269"/>
+      <c r="E39" s="269"/>
+      <c r="F39" s="269"/>
+      <c r="G39" s="269"/>
+      <c r="H39" s="269"/>
+      <c r="I39" s="269"/>
+      <c r="J39" s="269"/>
+      <c r="K39" s="270"/>
+    </row>
+    <row r="40" spans="2:11" ht="21" customHeight="1">
+      <c r="B40" s="284" t="s">
         <v>351</v>
       </c>
-      <c r="C38" s="262" t="s">
+      <c r="C40" s="268" t="s">
         <v>352</v>
       </c>
-      <c r="D38" s="263"/>
-      <c r="E38" s="263"/>
-      <c r="F38" s="263"/>
-      <c r="G38" s="263"/>
-      <c r="H38" s="264"/>
-      <c r="I38" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J38" s="262"/>
-      <c r="K38" s="264"/>
-    </row>
-    <row r="39" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B39" s="262" t="s">
+      <c r="D40" s="269"/>
+      <c r="E40" s="269"/>
+      <c r="F40" s="269"/>
+      <c r="G40" s="269"/>
+      <c r="H40" s="270"/>
+      <c r="I40" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J40" s="268"/>
+      <c r="K40" s="270"/>
+    </row>
+    <row r="41" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B41" s="284" t="s">
         <v>353</v>
       </c>
-      <c r="C39" s="263"/>
-      <c r="D39" s="263"/>
-      <c r="E39" s="263"/>
-      <c r="F39" s="263"/>
-      <c r="G39" s="263"/>
-      <c r="H39" s="263"/>
-      <c r="I39" s="263"/>
-      <c r="J39" s="263"/>
-      <c r="K39" s="264"/>
-    </row>
-    <row r="40" spans="2:11" ht="21" customHeight="1">
-      <c r="B40" s="278" t="s">
+      <c r="C41" s="268" t="s">
         <v>354</v>
       </c>
-      <c r="C40" s="262" t="s">
+      <c r="D41" s="269"/>
+      <c r="E41" s="269"/>
+      <c r="F41" s="269"/>
+      <c r="G41" s="269"/>
+      <c r="H41" s="270"/>
+      <c r="I41" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J41" s="268"/>
+      <c r="K41" s="270"/>
+    </row>
+    <row r="42" spans="2:11" ht="18.95" customHeight="1">
+      <c r="B42" s="284" t="s">
         <v>355</v>
       </c>
-      <c r="D40" s="263"/>
-      <c r="E40" s="263"/>
-      <c r="F40" s="263"/>
-      <c r="G40" s="263"/>
-      <c r="H40" s="264"/>
-      <c r="I40" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J40" s="262"/>
-      <c r="K40" s="264"/>
-    </row>
-    <row r="41" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B41" s="278" t="s">
+      <c r="C42" s="268" t="s">
         <v>356</v>
       </c>
-      <c r="C41" s="262" t="s">
+      <c r="D42" s="269"/>
+      <c r="E42" s="269"/>
+      <c r="F42" s="269"/>
+      <c r="G42" s="269"/>
+      <c r="H42" s="270"/>
+      <c r="I42" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J42" s="268"/>
+      <c r="K42" s="270"/>
+    </row>
+    <row r="43" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B43" s="284" t="s">
         <v>357</v>
       </c>
-      <c r="D41" s="263"/>
-      <c r="E41" s="263"/>
-      <c r="F41" s="263"/>
-      <c r="G41" s="263"/>
-      <c r="H41" s="264"/>
-      <c r="I41" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J41" s="262"/>
-      <c r="K41" s="264"/>
-    </row>
-    <row r="42" spans="2:11" ht="18.95" customHeight="1">
-      <c r="B42" s="278" t="s">
+      <c r="C43" s="268" t="s">
         <v>358</v>
       </c>
-      <c r="C42" s="262" t="s">
+      <c r="D43" s="269"/>
+      <c r="E43" s="269"/>
+      <c r="F43" s="269"/>
+      <c r="G43" s="269"/>
+      <c r="H43" s="270"/>
+      <c r="I43" s="261" t="s">
+        <v>311</v>
+      </c>
+      <c r="J43" s="268"/>
+      <c r="K43" s="270"/>
+    </row>
+    <row r="44" spans="2:11" ht="50.1" customHeight="1">
+      <c r="B44" s="268" t="s">
         <v>359</v>
       </c>
-      <c r="D42" s="263"/>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="263"/>
-      <c r="H42" s="264"/>
-      <c r="I42" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="262"/>
-      <c r="K42" s="264"/>
-    </row>
-    <row r="43" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B43" s="278" t="s">
-        <v>360</v>
-      </c>
-      <c r="C43" s="262" t="s">
-        <v>361</v>
-      </c>
-      <c r="D43" s="263"/>
-      <c r="E43" s="263"/>
-      <c r="F43" s="263"/>
-      <c r="G43" s="263"/>
-      <c r="H43" s="264"/>
-      <c r="I43" s="253" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="262"/>
-      <c r="K43" s="264"/>
-    </row>
-    <row r="44" spans="2:11" ht="50.1" customHeight="1">
-      <c r="B44" s="262" t="s">
-        <v>362</v>
-      </c>
-      <c r="C44" s="263"/>
-      <c r="D44" s="263"/>
-      <c r="E44" s="263"/>
-      <c r="F44" s="263"/>
-      <c r="G44" s="263"/>
-      <c r="H44" s="263"/>
-      <c r="I44" s="263"/>
-      <c r="J44" s="263"/>
-      <c r="K44" s="264"/>
+      <c r="C44" s="269"/>
+      <c r="D44" s="269"/>
+      <c r="E44" s="269"/>
+      <c r="F44" s="269"/>
+      <c r="G44" s="269"/>
+      <c r="H44" s="269"/>
+      <c r="I44" s="269"/>
+      <c r="J44" s="269"/>
+      <c r="K44" s="270"/>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="249"/>
-      <c r="C45" s="249"/>
-      <c r="D45" s="249"/>
-      <c r="E45" s="249"/>
-      <c r="F45" s="249"/>
-      <c r="G45" s="249"/>
-      <c r="H45" s="249"/>
-      <c r="I45" s="249"/>
-      <c r="J45" s="249"/>
-      <c r="K45" s="249"/>
+      <c r="B45" s="258"/>
+      <c r="C45" s="258"/>
+      <c r="D45" s="258"/>
+      <c r="E45" s="258"/>
+      <c r="F45" s="258"/>
+      <c r="G45" s="258"/>
+      <c r="H45" s="258"/>
+      <c r="I45" s="258"/>
+      <c r="J45" s="258"/>
+      <c r="K45" s="258"/>
     </row>
     <row r="46" spans="2:11" ht="11.1" customHeight="1"/>
   </sheetData>
@@ -10830,9 +10961,9 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:K4"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>